--- a/example/training/training_validation_reference.xlsx
+++ b/example/training/training_validation_reference.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Made on 2026-10-15 by openalaqs_standalone/validation/tools/regenerate_training_validation_xlsx.py</t>
+          <t>Made on 2026-10-19 by openalaqs_standalone/validation/tools/regenerate_training_validation_xlsx.py</t>
         </is>
       </c>
     </row>
@@ -745,16 +745,16 @@
         <v>22.44232213980615</v>
       </c>
       <c r="D3" t="n">
-        <v>23.69105554562599</v>
+        <v>23.69103872425993</v>
       </c>
       <c r="E3" t="n">
-        <v>23.69098956366105</v>
+        <v>23.69097274229499</v>
       </c>
       <c r="F3" t="n">
-        <v>21.98880741342589</v>
+        <v>21.98880331149084</v>
       </c>
       <c r="G3" t="n">
-        <v>21.98880741330721</v>
+        <v>21.98880331137216</v>
       </c>
       <c r="H3" t="n">
         <v>22.44232213988976</v>
@@ -776,10 +776,10 @@
         <v>7692.653143013189</v>
       </c>
       <c r="D4" t="n">
-        <v>5995.506861712011</v>
+        <v>5995.493517858697</v>
       </c>
       <c r="E4" t="n">
-        <v>5995.497961566793</v>
+        <v>5995.484617713478</v>
       </c>
       <c r="F4" t="n">
         <v>7698.001202660278</v>
@@ -807,16 +807,16 @@
         <v>1.228176479875784</v>
       </c>
       <c r="D5" t="n">
-        <v>1.25467737197027</v>
+        <v>1.254676962839943</v>
       </c>
       <c r="E5" t="n">
-        <v>1.254676487330285</v>
+        <v>1.254676078199959</v>
       </c>
       <c r="F5" t="n">
-        <v>1.237919939865066</v>
+        <v>1.237919806197084</v>
       </c>
       <c r="G5" t="n">
-        <v>1.237919939863747</v>
+        <v>1.237919806195764</v>
       </c>
       <c r="H5" t="n">
         <v>1.228176479876839</v>
@@ -838,16 +838,16 @@
         <v>31.80434781352288</v>
       </c>
       <c r="D6" t="n">
-        <v>17.4192590836771</v>
+        <v>17.41922260484354</v>
       </c>
       <c r="E6" t="n">
-        <v>17.4192484698944</v>
+        <v>17.41921199106084</v>
       </c>
       <c r="F6" t="n">
-        <v>30.02411658704424</v>
+        <v>30.02429320233029</v>
       </c>
       <c r="G6" t="n">
-        <v>30.02411658713778</v>
+        <v>30.02429320242384</v>
       </c>
       <c r="H6" t="n">
         <v>30.66097271340226</v>
@@ -900,10 +900,10 @@
         <v>0.3215592737403333</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2850280665466242</v>
+        <v>0.2850278100415673</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2850279208906891</v>
+        <v>0.2850276643856322</v>
       </c>
       <c r="F8" t="n">
         <v>0.3218622643385006</v>
@@ -1371,16 +1371,16 @@
         <v>1.378813062957872</v>
       </c>
       <c r="E4" t="n">
-        <v>1.632836108687644</v>
+        <v>1.632835873001475</v>
       </c>
       <c r="F4" t="n">
-        <v>1.632836108687604</v>
+        <v>1.632835873001435</v>
       </c>
       <c r="G4" t="n">
-        <v>1.430578190224422</v>
+        <v>1.430577879312127</v>
       </c>
       <c r="H4" t="n">
-        <v>1.430578190224394</v>
+        <v>1.4305778793121</v>
       </c>
       <c r="I4" t="n">
         <v>490.1490905873051</v>
@@ -1389,10 +1389,10 @@
         <v>490.1490905872779</v>
       </c>
       <c r="K4" t="n">
-        <v>405.6002735942009</v>
+        <v>405.6001768750213</v>
       </c>
       <c r="L4" t="n">
-        <v>405.6002735941806</v>
+        <v>405.6001768750009</v>
       </c>
       <c r="M4" t="n">
         <v>500.9344436657162</v>
@@ -1407,16 +1407,16 @@
         <v>0.01895165692061777</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02240262750928279</v>
+        <v>0.02240262415216688</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0224026275092822</v>
+        <v>0.02240262415216629</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01966059452878914</v>
+        <v>0.01966059014354284</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01966059452878874</v>
+        <v>0.01966059014354243</v>
       </c>
       <c r="U4" t="n">
         <v>1.146122365269231</v>
@@ -1425,16 +1425,16 @@
         <v>1.146122365269156</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8058825825540175</v>
+        <v>0.8058823641523013</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8058825825539704</v>
+        <v>0.8058823641522543</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.184691032503901</v>
+        <v>1.184691312222633</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.184691032503825</v>
+        <v>1.184691312222558</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1461,10 +1461,10 @@
         <v>0.0371297399700309</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0356701733078088</v>
+        <v>0.0356701716489414</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.03567017330780844</v>
+        <v>0.03567017164894105</v>
       </c>
       <c r="AK4" t="n">
         <v>0.03730528588133773</v>
@@ -1489,10 +1489,10 @@
         <v>1.215414648670441</v>
       </c>
       <c r="E5" t="n">
-        <v>1.228964404756249</v>
+        <v>1.228964391559613</v>
       </c>
       <c r="F5" t="n">
-        <v>1.228964404756246</v>
+        <v>1.22896439155961</v>
       </c>
       <c r="G5" t="n">
         <v>1.231490660925497</v>
@@ -1507,10 +1507,10 @@
         <v>619.2711847860359</v>
       </c>
       <c r="K5" t="n">
-        <v>597.2314934158225</v>
+        <v>597.2313179545814</v>
       </c>
       <c r="L5" t="n">
-        <v>597.2314934157953</v>
+        <v>597.2313179545544</v>
       </c>
       <c r="M5" t="n">
         <v>630.8203587259277</v>
@@ -1525,10 +1525,10 @@
         <v>0.01866143787839263</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0185463481622464</v>
+        <v>0.01854634710651549</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01854634816224621</v>
+        <v>0.0185463471065153</v>
       </c>
       <c r="S5" t="n">
         <v>0.01874844865578619</v>
@@ -1543,16 +1543,16 @@
         <v>4.181440045730512</v>
       </c>
       <c r="W5" t="n">
-        <v>2.690133798906125</v>
+        <v>2.690133029619891</v>
       </c>
       <c r="X5" t="n">
-        <v>2.690133798906038</v>
+        <v>2.690133029619804</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.479758886198886</v>
+        <v>3.479763630922297</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.479758886198887</v>
+        <v>3.479763630922298</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1579,10 +1579,10 @@
         <v>0.01025643025501766</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.009884811562016932</v>
+        <v>0.009884808647926655</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.009884811562016501</v>
+        <v>0.009884808647926223</v>
       </c>
       <c r="AK5" t="n">
         <v>0.0104444083628621</v>
@@ -1607,16 +1607,16 @@
         <v>2.45980104308333</v>
       </c>
       <c r="E6" t="n">
-        <v>2.575307391419545</v>
+        <v>2.575307142304503</v>
       </c>
       <c r="F6" t="n">
-        <v>2.575307391419543</v>
+        <v>2.575307142304502</v>
       </c>
       <c r="G6" t="n">
-        <v>2.546333450904249</v>
+        <v>2.546332895381979</v>
       </c>
       <c r="H6" t="n">
-        <v>2.546333450904188</v>
+        <v>2.546332895381917</v>
       </c>
       <c r="I6" t="n">
         <v>462.8226583969786</v>
@@ -1625,10 +1625,10 @@
         <v>462.8226583969372</v>
       </c>
       <c r="K6" t="n">
-        <v>461.6559774151352</v>
+        <v>461.6558377888711</v>
       </c>
       <c r="L6" t="n">
-        <v>461.655977415073</v>
+        <v>461.6558377888089</v>
       </c>
       <c r="M6" t="n">
         <v>473.3176054306242</v>
@@ -1643,16 +1643,16 @@
         <v>0.2091411063916697</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2178583462547879</v>
+        <v>0.2178583379569806</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2178583462547868</v>
+        <v>0.2178583379569796</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2146793119611571</v>
+        <v>0.2146792877065687</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2146793119611553</v>
+        <v>0.2146792877065669</v>
       </c>
       <c r="U6" t="n">
         <v>0.9520470525262248</v>
@@ -1661,16 +1661,16 @@
         <v>0.952047052526121</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9298337744460332</v>
+        <v>0.9298334427391807</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9298337744458298</v>
+        <v>0.9298334427389773</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9760937360395266</v>
+        <v>0.9760940509823315</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9760937360394233</v>
+        <v>0.976094050982228</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1697,10 +1697,10 @@
         <v>0.02354209652469201</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.02359302719960514</v>
+        <v>0.02359302466415088</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.02359302719960401</v>
+        <v>0.02359302466414975</v>
       </c>
       <c r="AK6" t="n">
         <v>0.02380478910984933</v>
@@ -1725,10 +1725,10 @@
         <v>2.345789062664481</v>
       </c>
       <c r="E7" t="n">
-        <v>2.326634881479016</v>
+        <v>2.326634843410316</v>
       </c>
       <c r="F7" t="n">
-        <v>2.326634881478995</v>
+        <v>2.326634843410295</v>
       </c>
       <c r="G7" t="n">
         <v>2.364219089796888</v>
@@ -1743,10 +1743,10 @@
         <v>684.9000076076752</v>
       </c>
       <c r="K7" t="n">
-        <v>545.5515383252737</v>
+        <v>545.5513858680839</v>
       </c>
       <c r="L7" t="n">
-        <v>545.5515383251936</v>
+        <v>545.5513858680039</v>
       </c>
       <c r="M7" t="n">
         <v>696.0684395496039</v>
@@ -1761,10 +1761,10 @@
         <v>0.2216070221405297</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2230321114659493</v>
+        <v>0.2230321082553361</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2230321114659476</v>
+        <v>0.2230321082553343</v>
       </c>
       <c r="S7" t="n">
         <v>0.2262018639746856</v>
@@ -1779,16 +1779,16 @@
         <v>3.321360497066411</v>
       </c>
       <c r="W7" t="n">
-        <v>1.933417833204721</v>
+        <v>1.933417175669148</v>
       </c>
       <c r="X7" t="n">
-        <v>1.933417833204258</v>
+        <v>1.933417175668684</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.338618646681165</v>
+        <v>3.338619877407671</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.338618646680629</v>
+        <v>3.338619877407135</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0.02467646364099569</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.01900975608365796</v>
+        <v>0.01900975023442091</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01900975608365449</v>
+        <v>0.01900975023441744</v>
       </c>
       <c r="AK7" t="n">
         <v>0.02495601381400573</v>
@@ -1843,16 +1843,16 @@
         <v>1.378813062957872</v>
       </c>
       <c r="E8" t="n">
-        <v>1.625027207607039</v>
+        <v>1.625026308993482</v>
       </c>
       <c r="F8" t="n">
-        <v>1.625027207606999</v>
+        <v>1.625026308993442</v>
       </c>
       <c r="G8" t="n">
-        <v>1.417961374104755</v>
+        <v>1.417960210674832</v>
       </c>
       <c r="H8" t="n">
-        <v>1.417961374104728</v>
+        <v>1.417960210674805</v>
       </c>
       <c r="I8" t="n">
         <v>490.1490905873051</v>
@@ -1861,10 +1861,10 @@
         <v>490.1490905872779</v>
       </c>
       <c r="K8" t="n">
-        <v>399.8050190107323</v>
+        <v>399.8046537772933</v>
       </c>
       <c r="L8" t="n">
-        <v>399.8050190107122</v>
+        <v>399.8046537772732</v>
       </c>
       <c r="M8" t="n">
         <v>498.4702486717957</v>
@@ -1879,16 +1879,16 @@
         <v>0.01895165692061777</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02229551292661476</v>
+        <v>0.02229550012676938</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02229551292661417</v>
+        <v>0.02229550012676879</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01948880720982332</v>
+        <v>0.0194887907696156</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01948880720982292</v>
+        <v>0.0194887907696152</v>
       </c>
       <c r="U8" t="n">
         <v>1.146122365269231</v>
@@ -1897,16 +1897,16 @@
         <v>1.146122365269156</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8004768229391465</v>
+        <v>0.8004759918700028</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8004768229390997</v>
+        <v>0.8004759918699562</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.199335862818289</v>
+        <v>1.199336953562032</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.199335862818212</v>
+        <v>1.199336953561955</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1933,10 +1933,10 @@
         <v>0.0371297399700309</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.03557293300069914</v>
+        <v>0.03557292673644164</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0355729330006988</v>
+        <v>0.0355729267364413</v>
       </c>
       <c r="AK8" t="n">
         <v>0.03726517784289898</v>
@@ -1961,10 +1961,10 @@
         <v>1.231587047854708</v>
       </c>
       <c r="E9" t="n">
-        <v>1.235926849119978</v>
+        <v>1.235926748212021</v>
       </c>
       <c r="F9" t="n">
-        <v>1.235926849119993</v>
+        <v>1.235926748212036</v>
       </c>
       <c r="G9" t="n">
         <v>1.240978847230464</v>
@@ -1979,10 +1979,10 @@
         <v>815.8280364102174</v>
       </c>
       <c r="K9" t="n">
-        <v>758.2104078741677</v>
+        <v>758.2090790506487</v>
       </c>
       <c r="L9" t="n">
-        <v>758.2104078743794</v>
+        <v>758.2090790508603</v>
       </c>
       <c r="M9" t="n">
         <v>824.7385005737856</v>
@@ -1997,10 +1997,10 @@
         <v>0.01990546858487479</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0194870876477196</v>
+        <v>0.01948707957508305</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01948708764772086</v>
+        <v>0.01948707957508431</v>
       </c>
       <c r="S9" t="n">
         <v>0.01989124749655848</v>
@@ -2015,16 +2015,16 @@
         <v>5.013696588367762</v>
       </c>
       <c r="W9" t="n">
-        <v>3.384692152787725</v>
+        <v>3.38468643062121</v>
       </c>
       <c r="X9" t="n">
-        <v>3.384692152789462</v>
+        <v>3.384686430622946</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.568379702780811</v>
+        <v>4.568400569645822</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.568379702782324</v>
+        <v>4.568400569647335</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -2051,10 +2051,10 @@
         <v>0.01347319579547339</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.01251774411385746</v>
+        <v>0.0125177222061523</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01251774411386098</v>
+        <v>0.01251772220615583</v>
       </c>
       <c r="AK9" t="n">
         <v>0.01361822540557363</v>
@@ -2079,16 +2079,16 @@
         <v>2.45980104308333</v>
       </c>
       <c r="E10" t="n">
-        <v>2.562967276541073</v>
+        <v>2.562966326706932</v>
       </c>
       <c r="F10" t="n">
-        <v>2.562967276541072</v>
+        <v>2.56296632670693</v>
       </c>
       <c r="G10" t="n">
-        <v>2.524466071009253</v>
+        <v>2.524463998938689</v>
       </c>
       <c r="H10" t="n">
-        <v>2.524466071009193</v>
+        <v>2.524463998938629</v>
       </c>
       <c r="I10" t="n">
         <v>462.8226583969787</v>
@@ -2097,10 +2097,10 @@
         <v>462.8226583969372</v>
       </c>
       <c r="K10" t="n">
-        <v>455.065503013417</v>
+        <v>455.0649757409302</v>
       </c>
       <c r="L10" t="n">
-        <v>455.0655030133557</v>
+        <v>455.0649757408688</v>
       </c>
       <c r="M10" t="n">
         <v>470.9197612660657</v>
@@ -2115,16 +2115,16 @@
         <v>0.2091411063916697</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.216811940154692</v>
+        <v>0.2168119085164784</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2168119401546909</v>
+        <v>0.2168119085164773</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2131294018673473</v>
+        <v>0.2131293132794072</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2131294018673456</v>
+        <v>0.2131293132794056</v>
       </c>
       <c r="U10" t="n">
         <v>0.952047052526225</v>
@@ -2133,16 +2133,16 @@
         <v>0.952047052526121</v>
       </c>
       <c r="W10" t="n">
-        <v>0.9236120904142044</v>
+        <v>0.9236108281642439</v>
       </c>
       <c r="X10" t="n">
-        <v>0.9236120904140023</v>
+        <v>0.9236108281640419</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.9898651678339773</v>
+        <v>0.9898663981330998</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.9898651678338718</v>
+        <v>0.989866398132994</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -2169,10 +2169,10 @@
         <v>0.02354209652469201</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.02345687483255139</v>
+        <v>0.02345686525788232</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.02345687483255027</v>
+        <v>0.02345686525788121</v>
       </c>
       <c r="AK10" t="n">
         <v>0.02374477014259098</v>
@@ -2197,10 +2197,10 @@
         <v>2.40164085935612</v>
       </c>
       <c r="E11" t="n">
-        <v>2.354305938832664</v>
+        <v>2.354305633160197</v>
       </c>
       <c r="F11" t="n">
-        <v>2.354305938832648</v>
+        <v>2.354305633160181</v>
       </c>
       <c r="G11" t="n">
         <v>2.412504918955086</v>
@@ -2215,10 +2215,10 @@
         <v>914.1099784460888</v>
       </c>
       <c r="K11" t="n">
-        <v>691.8823759728303</v>
+        <v>691.8811635331762</v>
       </c>
       <c r="L11" t="n">
-        <v>691.8823759727701</v>
+        <v>691.8811635331159</v>
       </c>
       <c r="M11" t="n">
         <v>922.7266910441036</v>
@@ -2233,10 +2233,10 @@
         <v>0.2281351542213706</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2252368439313496</v>
+        <v>0.225236818151744</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2252368439313483</v>
+        <v>0.2252368181517426</v>
       </c>
       <c r="S11" t="n">
         <v>0.2301451916525176</v>
@@ -2251,16 +2251,16 @@
         <v>4.497874967635738</v>
       </c>
       <c r="W11" t="n">
-        <v>2.55713926240638</v>
+        <v>2.557134138059788</v>
       </c>
       <c r="X11" t="n">
-        <v>2.55713926240608</v>
+        <v>2.557134138059487</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.632056058129776</v>
+        <v>4.632064213363097</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.632056058129357</v>
+        <v>4.632064213362678</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2287,10 +2287,10 @@
         <v>0.03259013181614914</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.02405956924810905</v>
+        <v>0.0240595251764346</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.02405956924810679</v>
+        <v>0.02405952517643234</v>
       </c>
       <c r="AK11" t="n">
         <v>0.03280581146662055</v>
@@ -2315,10 +2315,10 @@
         <v>1.341212842926714</v>
       </c>
       <c r="E12" t="n">
-        <v>1.479710595352891</v>
+        <v>1.479706289942876</v>
       </c>
       <c r="F12" t="n">
-        <v>1.479710595352851</v>
+        <v>1.479706289942836</v>
       </c>
       <c r="G12" t="n">
         <v>1.114410376065972</v>
@@ -2333,10 +2333,10 @@
         <v>445.3126017954071</v>
       </c>
       <c r="K12" t="n">
-        <v>331.9477636192732</v>
+        <v>331.9457703044816</v>
       </c>
       <c r="L12" t="n">
-        <v>331.9477636192559</v>
+        <v>331.9457703044641</v>
       </c>
       <c r="M12" t="n">
         <v>431.2239001263054</v>
@@ -2351,10 +2351,10 @@
         <v>0.01838410642958143</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02033677886110626</v>
+        <v>0.02033671589172297</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02033677886110568</v>
+        <v>0.0203367158917224</v>
       </c>
       <c r="S12" t="n">
         <v>0.01656282724585744</v>
@@ -2369,16 +2369,16 @@
         <v>1.021970695354957</v>
       </c>
       <c r="W12" t="n">
-        <v>0.512485019081269</v>
+        <v>0.5124814119682357</v>
       </c>
       <c r="X12" t="n">
-        <v>0.512485019081238</v>
+        <v>0.5124814119682047</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.8395373853507221</v>
+        <v>0.8395402819178565</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.8395373853506585</v>
+        <v>0.839540281917793</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2405,10 +2405,10 @@
         <v>0.03636073231494269</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0344286972909495</v>
+        <v>0.03442866310285014</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0344286972909492</v>
+        <v>0.03442866310284985</v>
       </c>
       <c r="AK12" t="n">
         <v>0.03613142002858127</v>
@@ -2433,10 +2433,10 @@
         <v>1.209859455960507</v>
       </c>
       <c r="E13" t="n">
-        <v>1.193107801363486</v>
+        <v>1.193107555204878</v>
       </c>
       <c r="F13" t="n">
-        <v>1.193107801363481</v>
+        <v>1.193107555204873</v>
       </c>
       <c r="G13" t="n">
         <v>1.199751393988662</v>
@@ -2451,10 +2451,10 @@
         <v>551.7542272345349</v>
       </c>
       <c r="K13" t="n">
-        <v>459.1334183706381</v>
+        <v>459.1305455656839</v>
       </c>
       <c r="L13" t="n">
-        <v>459.1334183705916</v>
+        <v>459.1305455656374</v>
       </c>
       <c r="M13" t="n">
         <v>536.6677608963153</v>
@@ -2469,10 +2469,10 @@
         <v>0.01823411536224389</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01771778275481096</v>
+        <v>0.01771776306212235</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01771778275481064</v>
+        <v>0.01771776306212201</v>
       </c>
       <c r="S13" t="n">
         <v>0.01824927016482503</v>
@@ -2487,16 +2487,16 @@
         <v>3.895561282427357</v>
       </c>
       <c r="W13" t="n">
-        <v>1.602837718187557</v>
+        <v>1.602827862214278</v>
       </c>
       <c r="X13" t="n">
-        <v>1.602837718187034</v>
+        <v>1.602827862213756</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.183773462739392</v>
+        <v>3.183778641457233</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.183773462739182</v>
+        <v>3.183778641457023</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2523,10 +2523,10 @@
         <v>0.009151476544915844</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.007608769150910512</v>
+        <v>0.007608721141722933</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.007608769150909741</v>
+        <v>0.007608721141722161</v>
       </c>
       <c r="AK13" t="n">
         <v>0.008905924316585314</v>
@@ -2605,16 +2605,16 @@
         <v>3.836516818567063</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2440459320356642</v>
+        <v>0.2440459320356641</v>
       </c>
       <c r="X14" t="n">
         <v>0.2440353181297802</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.109108633955858</v>
+        <v>4.109231807499004</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.109108633955858</v>
+        <v>4.109231807499004</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2669,10 +2669,10 @@
         <v>2.410241413919331</v>
       </c>
       <c r="E15" t="n">
-        <v>2.439657098338885</v>
+        <v>2.439651908550792</v>
       </c>
       <c r="F15" t="n">
-        <v>2.439657098338884</v>
+        <v>2.439651908550791</v>
       </c>
       <c r="G15" t="n">
         <v>2.122365661439178</v>
@@ -2687,10 +2687,10 @@
         <v>423.8653379595651</v>
       </c>
       <c r="K15" t="n">
-        <v>366.6436653684529</v>
+        <v>366.6409866467207</v>
       </c>
       <c r="L15" t="n">
-        <v>366.6436653683997</v>
+        <v>366.6409866466675</v>
       </c>
       <c r="M15" t="n">
         <v>410.1559881853913</v>
@@ -2705,10 +2705,10 @@
         <v>0.2079082797955503</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.209852087574754</v>
+        <v>0.209851916968827</v>
       </c>
       <c r="R15" t="n">
-        <v>0.209852087574753</v>
+        <v>0.209851916968826</v>
       </c>
       <c r="S15" t="n">
         <v>0.2035436216765866</v>
@@ -2723,16 +2723,16 @@
         <v>0.854160620794243</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5640030163257768</v>
+        <v>0.5639980441006247</v>
       </c>
       <c r="X15" t="n">
-        <v>0.5640030163256429</v>
+        <v>0.5639980441004906</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.7150696598002436</v>
+        <v>0.7150743687008665</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.7150696598001542</v>
+        <v>0.7150743687007772</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2759,10 +2759,10 @@
         <v>0.02283467586414139</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.02170139120802857</v>
+        <v>0.02170134256548653</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.02170139120802761</v>
+        <v>0.02170134256548556</v>
       </c>
       <c r="AK15" t="n">
         <v>0.02249152553461129</v>
@@ -2787,10 +2787,10 @@
         <v>1.369366794259893</v>
       </c>
       <c r="E16" t="n">
-        <v>1.519486932405388</v>
+        <v>1.519482643490708</v>
       </c>
       <c r="F16" t="n">
-        <v>1.519486932287693</v>
+        <v>1.519482643373014</v>
       </c>
       <c r="G16" t="n">
         <v>1.154442898835607</v>
@@ -2805,10 +2805,10 @@
         <v>435.0134425595875</v>
       </c>
       <c r="K16" t="n">
-        <v>318.1371235221576</v>
+        <v>318.1353225432958</v>
       </c>
       <c r="L16" t="n">
-        <v>318.1371235629618</v>
+        <v>318.1353225840994</v>
       </c>
       <c r="M16" t="n">
         <v>420.3891426172511</v>
@@ -2823,10 +2823,10 @@
         <v>0.01873833828014877</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0207593736442275</v>
+        <v>0.02075931199346882</v>
       </c>
       <c r="R16" t="n">
-        <v>0.02075937364297673</v>
+        <v>0.02075931199221805</v>
       </c>
       <c r="S16" t="n">
         <v>0.01700583638973179</v>
@@ -2841,16 +2841,16 @@
         <v>0.9854274619882872</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4706990803884775</v>
+        <v>0.4706959536289703</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4706990805119657</v>
+        <v>0.4706959537524571</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.8078283522116888</v>
+        <v>0.8078310965163508</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.8078283523053967</v>
+        <v>0.8078310966100591</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2877,10 +2877,10 @@
         <v>0.03617872749814146</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.03418693440960546</v>
+        <v>0.03418690352033271</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.03418693441031979</v>
+        <v>0.03418690352104702</v>
       </c>
       <c r="AK16" t="n">
         <v>0.03594069764020458</v>
@@ -2903,16 +2903,16 @@
         <v>22.44232213980615</v>
       </c>
       <c r="E17" t="n">
-        <v>23.69105554562599</v>
+        <v>23.69103872425993</v>
       </c>
       <c r="F17" t="n">
-        <v>23.69098956366105</v>
+        <v>23.69097274229499</v>
       </c>
       <c r="G17" t="n">
-        <v>21.98880741342589</v>
+        <v>21.98880331149084</v>
       </c>
       <c r="H17" t="n">
-        <v>21.98880741330721</v>
+        <v>21.98880331137216</v>
       </c>
       <c r="I17" t="n">
         <v>7692.653142982975</v>
@@ -2921,10 +2921,10 @@
         <v>7692.653143013189</v>
       </c>
       <c r="K17" t="n">
-        <v>5995.506861712011</v>
+        <v>5995.493517858697</v>
       </c>
       <c r="L17" t="n">
-        <v>5995.497961566793</v>
+        <v>5995.484617713478</v>
       </c>
       <c r="M17" t="n">
         <v>7698.001202660278</v>
@@ -2939,16 +2939,16 @@
         <v>1.228176479875784</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.25467737197027</v>
+        <v>1.254676962839943</v>
       </c>
       <c r="R17" t="n">
-        <v>1.254676487330285</v>
+        <v>1.254676078199959</v>
       </c>
       <c r="S17" t="n">
-        <v>1.237919939865066</v>
+        <v>1.237919806197084</v>
       </c>
       <c r="T17" t="n">
-        <v>1.237919939863747</v>
+        <v>1.237919806195764</v>
       </c>
       <c r="U17" t="n">
         <v>31.80434781341469</v>
@@ -2957,16 +2957,16 @@
         <v>31.80434781352288</v>
       </c>
       <c r="W17" t="n">
-        <v>17.4192590836771</v>
+        <v>17.41922260484354</v>
       </c>
       <c r="X17" t="n">
-        <v>17.4192484698944</v>
+        <v>17.41921199106084</v>
       </c>
       <c r="Y17" t="n">
-        <v>30.02411658704424</v>
+        <v>30.02429320233029</v>
       </c>
       <c r="Z17" t="n">
-        <v>30.02411658713778</v>
+        <v>30.02429320242384</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2993,10 +2993,10 @@
         <v>0.3215592737403333</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.2850280665466242</v>
+        <v>0.2850278100415673</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.2850279208906891</v>
+        <v>0.2850276643856322</v>
       </c>
       <c r="AK17" t="n">
         <v>0.3218622643385006</v>
@@ -3594,16 +3594,16 @@
         <v>5.054028754711721</v>
       </c>
       <c r="C4" t="n">
-        <v>5.437107904863439</v>
+        <v>5.437107406865591</v>
       </c>
       <c r="D4" t="n">
-        <v>5.208402302054168</v>
+        <v>5.208401435619603</v>
       </c>
       <c r="E4" t="n">
         <v>1572.242933770347</v>
       </c>
       <c r="F4" t="n">
-        <v>1464.487744425159</v>
+        <v>1464.487332618474</v>
       </c>
       <c r="G4" t="n">
         <v>1605.072407822268</v>
@@ -3612,19 +3612,19 @@
         <v>0.246754201190682</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2588073219263171</v>
+        <v>0.258807309215663</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2530883551457324</v>
+        <v>0.2530883265058977</v>
       </c>
       <c r="K4" t="n">
         <v>6.279609463525886</v>
       </c>
       <c r="L4" t="n">
-        <v>4.425850155906176</v>
+        <v>4.425848836511372</v>
       </c>
       <c r="M4" t="n">
-        <v>5.640543654742314</v>
+        <v>5.640548994127261</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -3639,7 +3639,7 @@
         <v>0.07092826674974223</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06914801206943087</v>
+        <v>0.06914800496101894</v>
       </c>
       <c r="S4" t="n">
         <v>0.07155448335404917</v>
@@ -3655,7 +3655,7 @@
         <v>2.345789062664506</v>
       </c>
       <c r="C5" t="n">
-        <v>2.326634881479016</v>
+        <v>2.326634843410316</v>
       </c>
       <c r="D5" t="n">
         <v>2.364219089796888</v>
@@ -3664,7 +3664,7 @@
         <v>684.9000076077568</v>
       </c>
       <c r="F5" t="n">
-        <v>545.5515383252737</v>
+        <v>545.5513858680839</v>
       </c>
       <c r="G5" t="n">
         <v>696.0684395496039</v>
@@ -3673,7 +3673,7 @@
         <v>0.2216070221405304</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2230321114659493</v>
+        <v>0.2230321082553361</v>
       </c>
       <c r="J5" t="n">
         <v>0.2262018639746856</v>
@@ -3682,10 +3682,10 @@
         <v>3.321360497066971</v>
       </c>
       <c r="L5" t="n">
-        <v>1.933417833204721</v>
+        <v>1.933417175669148</v>
       </c>
       <c r="M5" t="n">
-        <v>3.338618646681165</v>
+        <v>3.338619877407671</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -3700,7 +3700,7 @@
         <v>0.0246764636409993</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01900975608365796</v>
+        <v>0.01900975023442091</v>
       </c>
       <c r="S5" t="n">
         <v>0.02495601381400573</v>
@@ -3716,16 +3716,16 @@
         <v>2.610400110812586</v>
       </c>
       <c r="C6" t="n">
-        <v>2.860954056727017</v>
+        <v>2.860953057205503</v>
       </c>
       <c r="D6" t="n">
-        <v>2.658940221335219</v>
+        <v>2.658939057905296</v>
       </c>
       <c r="E6" t="n">
         <v>1305.977126997311</v>
       </c>
       <c r="F6" t="n">
-        <v>1158.0154268849</v>
+        <v>1158.013732827942</v>
       </c>
       <c r="G6" t="n">
         <v>1323.208749245581</v>
@@ -3734,19 +3734,19 @@
         <v>0.03885712550549156</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04178260057433436</v>
+        <v>0.04178257970185242</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0393800547063818</v>
+        <v>0.03938003826617407</v>
       </c>
       <c r="K6" t="n">
         <v>6.159818953635167</v>
       </c>
       <c r="L6" t="n">
-        <v>4.185168975726872</v>
+        <v>4.185162422491213</v>
       </c>
       <c r="M6" t="n">
-        <v>5.7677155655991</v>
+        <v>5.767737523207854</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -3761,7 +3761,7 @@
         <v>0.05060293576550123</v>
       </c>
       <c r="R6" t="n">
-        <v>0.04809067711455659</v>
+        <v>0.04809064894259394</v>
       </c>
       <c r="S6" t="n">
         <v>0.05088340324847261</v>
@@ -3777,16 +3777,16 @@
         <v>4.861441902439521</v>
       </c>
       <c r="C7" t="n">
-        <v>4.917273215373736</v>
+        <v>4.917271959867128</v>
       </c>
       <c r="D7" t="n">
-        <v>4.936970989964339</v>
+        <v>4.936968917893775</v>
       </c>
       <c r="E7" t="n">
         <v>1376.932636843142</v>
       </c>
       <c r="F7" t="n">
-        <v>1146.947878986247</v>
+        <v>1146.946139274106</v>
       </c>
       <c r="G7" t="n">
         <v>1393.646452310169</v>
@@ -3795,19 +3795,19 @@
         <v>0.4372762606130435</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4420487840860416</v>
+        <v>0.4420487266682223</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4432745935198649</v>
+        <v>0.4432745049319249</v>
       </c>
       <c r="K7" t="n">
         <v>5.44992202016237</v>
       </c>
       <c r="L7" t="n">
-        <v>3.480751352820584</v>
+        <v>3.480744966224032</v>
       </c>
       <c r="M7" t="n">
-        <v>5.621921225963753</v>
+        <v>5.621930611496197</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0.05613222834084461</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04751644408066044</v>
+        <v>0.04751639043431692</v>
       </c>
       <c r="S7" t="n">
         <v>0.05655058160921153</v>
@@ -3838,7 +3838,7 @@
         <v>2.551072298887246</v>
       </c>
       <c r="C8" t="n">
-        <v>2.672818396716377</v>
+        <v>2.672813845147754</v>
       </c>
       <c r="D8" t="n">
         <v>2.314161770054634</v>
@@ -3847,7 +3847,7 @@
         <v>997.0668290300034</v>
       </c>
       <c r="F8" t="n">
-        <v>791.0811819899113</v>
+        <v>791.0763158701654</v>
       </c>
       <c r="G8" t="n">
         <v>967.8916610226206</v>
@@ -3856,7 +3856,7 @@
         <v>0.03661822179182588</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03805456161591722</v>
+        <v>0.03805447895384531</v>
       </c>
       <c r="J8" t="n">
         <v>0.03481209741068246</v>
@@ -3865,10 +3865,10 @@
         <v>4.917531977782594</v>
       </c>
       <c r="L8" t="n">
-        <v>2.115322737268825</v>
+        <v>2.115309274182514</v>
       </c>
       <c r="M8" t="n">
-        <v>4.023310848090114</v>
+        <v>4.02331892337509</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>0.04551220885985956</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04203746644186002</v>
+        <v>0.04203738424457307</v>
       </c>
       <c r="S8" t="n">
         <v>0.04503734434516658</v>
@@ -3899,7 +3899,7 @@
         <v>3.65022321603094</v>
       </c>
       <c r="C9" t="n">
-        <v>3.956780158061019</v>
+        <v>3.956774968272925</v>
       </c>
       <c r="D9" t="n">
         <v>3.351670141385034</v>
@@ -3908,7 +3908,7 @@
         <v>1320.520166205253</v>
       </c>
       <c r="F9" t="n">
-        <v>571.2859675783628</v>
+        <v>571.2832888566306</v>
       </c>
       <c r="G9" t="n">
         <v>1291.724350092784</v>
@@ -3917,7 +3917,7 @@
         <v>0.2283253103540685</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2301926186574826</v>
+        <v>0.2301924480515556</v>
       </c>
       <c r="J9" t="n">
         <v>0.2241571387179871</v>
@@ -3926,10 +3926,10 @@
         <v>4.69067743936141</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8080489483614409</v>
+        <v>0.8080439761362889</v>
       </c>
       <c r="M9" t="n">
-        <v>4.824178293756102</v>
+        <v>4.824306176199871</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0.03752844288525238</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02503877634685287</v>
+        <v>0.02503872770431084</v>
       </c>
       <c r="S9" t="n">
         <v>0.03693974032739044</v>
@@ -3960,7 +3960,7 @@
         <v>1.369366794343237</v>
       </c>
       <c r="C10" t="n">
-        <v>1.519486932405388</v>
+        <v>1.519482643490708</v>
       </c>
       <c r="D10" t="n">
         <v>1.154442898835607</v>
@@ -3969,7 +3969,7 @@
         <v>435.0134425291626</v>
       </c>
       <c r="F10" t="n">
-        <v>318.1371235221576</v>
+        <v>318.1353225432958</v>
       </c>
       <c r="G10" t="n">
         <v>420.3891426172511</v>
@@ -3978,7 +3978,7 @@
         <v>0.0187383382811975</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0207593736442275</v>
+        <v>0.02075931199346882</v>
       </c>
       <c r="J10" t="n">
         <v>0.01700583638973179</v>
@@ -3987,10 +3987,10 @@
         <v>0.9854274618802966</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4706990803884775</v>
+        <v>0.4706959536289703</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8078283522116888</v>
+        <v>0.8078310965163508</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
         <v>0.03617872749760378</v>
       </c>
       <c r="R10" t="n">
-        <v>0.03418693440960546</v>
+        <v>0.03418690352033271</v>
       </c>
       <c r="S10" t="n">
         <v>0.03594069764020458</v>

--- a/example/training/training_validation_reference.xlsx
+++ b/example/training/training_validation_reference.xlsx
@@ -490,7 +490,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Worst relative gap plugin vs reference: 2.6e-10 on the ANP movements, 4.4e-05 on movement 11 (CUSTOM profile, supplied track).</t>
+          <t>Worst relative gap plugin vs reference: 2.4e-13 on the ANP movements, 4.4e-05 on movement 11 (CUSTOM profile, supplied track).</t>
         </is>
       </c>
     </row>
@@ -739,28 +739,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.44232213988976</v>
+        <v>22.41416778264819</v>
       </c>
       <c r="C3" t="n">
-        <v>22.44232213980615</v>
+        <v>22.41416778264804</v>
       </c>
       <c r="D3" t="n">
-        <v>23.69103872425993</v>
+        <v>23.65126116177226</v>
       </c>
       <c r="E3" t="n">
-        <v>23.69097274229499</v>
+        <v>23.65119517992509</v>
       </c>
       <c r="F3" t="n">
-        <v>21.98880331149084</v>
+        <v>21.94877074704628</v>
       </c>
       <c r="G3" t="n">
-        <v>21.98880331137216</v>
+        <v>21.94877074704612</v>
       </c>
       <c r="H3" t="n">
-        <v>22.44232213988976</v>
+        <v>22.41416778264819</v>
       </c>
       <c r="I3" t="n">
-        <v>22.44232213980615</v>
+        <v>22.41416778264804</v>
       </c>
     </row>
     <row r="4">
@@ -770,28 +770,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7692.653142982975</v>
+        <v>7702.951816940053</v>
       </c>
       <c r="C4" t="n">
-        <v>7692.653143013189</v>
+        <v>7702.95181693998</v>
       </c>
       <c r="D4" t="n">
-        <v>5995.493517858697</v>
+        <v>6009.303801314025</v>
       </c>
       <c r="E4" t="n">
-        <v>5995.484617713478</v>
+        <v>6009.294901128162</v>
       </c>
       <c r="F4" t="n">
-        <v>7698.001202660278</v>
+        <v>7708.835474860139</v>
       </c>
       <c r="G4" t="n">
-        <v>7698.001202692075</v>
+        <v>7708.835474860065</v>
       </c>
       <c r="H4" t="n">
-        <v>7692.653142982975</v>
+        <v>7702.951816940053</v>
       </c>
       <c r="I4" t="n">
-        <v>7692.653143013189</v>
+        <v>7702.95181693998</v>
       </c>
     </row>
     <row r="5">
@@ -801,28 +801,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.228176479876839</v>
+        <v>1.227822241879152</v>
       </c>
       <c r="C5" t="n">
-        <v>1.228176479875784</v>
+        <v>1.227822241879149</v>
       </c>
       <c r="D5" t="n">
-        <v>1.254676962839943</v>
+        <v>1.2542543505182</v>
       </c>
       <c r="E5" t="n">
-        <v>1.254676078199959</v>
+        <v>1.254253465879471</v>
       </c>
       <c r="F5" t="n">
-        <v>1.237919806197084</v>
+        <v>1.237476793718553</v>
       </c>
       <c r="G5" t="n">
-        <v>1.237919806195764</v>
+        <v>1.23747679371855</v>
       </c>
       <c r="H5" t="n">
-        <v>1.228176479876839</v>
+        <v>1.227822241879152</v>
       </c>
       <c r="I5" t="n">
-        <v>1.228176479875784</v>
+        <v>1.227822241879149</v>
       </c>
     </row>
     <row r="6">
@@ -832,28 +832,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.80434781341469</v>
+        <v>31.84088970009331</v>
       </c>
       <c r="C6" t="n">
-        <v>31.80434781352288</v>
+        <v>31.84088970009263</v>
       </c>
       <c r="D6" t="n">
-        <v>17.41922260484354</v>
+        <v>17.4610078635899</v>
       </c>
       <c r="E6" t="n">
-        <v>17.41921199106084</v>
+        <v>17.46099724968429</v>
       </c>
       <c r="F6" t="n">
-        <v>30.02429320233029</v>
+        <v>30.05600124882837</v>
       </c>
       <c r="G6" t="n">
-        <v>30.02429320242384</v>
+        <v>30.05600124882807</v>
       </c>
       <c r="H6" t="n">
-        <v>30.66097271340226</v>
+        <v>30.69751460020806</v>
       </c>
       <c r="I6" t="n">
-        <v>30.66093628291471</v>
+        <v>30.69747816961168</v>
       </c>
     </row>
     <row r="7">
@@ -894,28 +894,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3215592737398031</v>
+        <v>0.321741270223709</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3215592737403333</v>
+        <v>0.3217412702237114</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2850278100415673</v>
+        <v>0.2852695667998996</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2850276643856322</v>
+        <v>0.2852694211432593</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3218622643385006</v>
+        <v>0.3220529783934438</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3218622643390567</v>
+        <v>0.3220529783934462</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3215592737398031</v>
+        <v>0.321741270223709</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3215592737403333</v>
+        <v>0.3217412702237114</v>
       </c>
     </row>
   </sheetData>
@@ -1483,76 +1483,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.215414648670444</v>
+        <v>1.21541464867044</v>
       </c>
       <c r="D5" t="n">
-        <v>1.215414648670441</v>
+        <v>1.215414648670439</v>
       </c>
       <c r="E5" t="n">
-        <v>1.228964391559613</v>
+        <v>1.228964391559609</v>
       </c>
       <c r="F5" t="n">
-        <v>1.22896439155961</v>
+        <v>1.228964391559607</v>
       </c>
       <c r="G5" t="n">
-        <v>1.231490660925497</v>
+        <v>1.231490660925493</v>
       </c>
       <c r="H5" t="n">
-        <v>1.231490660925493</v>
+        <v>1.231490660925491</v>
       </c>
       <c r="I5" t="n">
-        <v>619.271184786063</v>
+        <v>619.2711847860185</v>
       </c>
       <c r="J5" t="n">
-        <v>619.2711847860359</v>
+        <v>619.2711847860041</v>
       </c>
       <c r="K5" t="n">
-        <v>597.2313179545814</v>
+        <v>597.2313179545268</v>
       </c>
       <c r="L5" t="n">
-        <v>597.2313179545544</v>
+        <v>597.2313179545213</v>
       </c>
       <c r="M5" t="n">
-        <v>630.8203587259277</v>
+        <v>630.8203587258831</v>
       </c>
       <c r="N5" t="n">
-        <v>630.8203587259003</v>
+        <v>630.8203587258687</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01866143787839281</v>
+        <v>0.01866143787839252</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01866143787839263</v>
+        <v>0.01866143787839243</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01854634710651549</v>
+        <v>0.01854634710651515</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0185463471065153</v>
+        <v>0.0185463471065151</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01874844865578619</v>
+        <v>0.01874844865578592</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01874844865578601</v>
+        <v>0.01874844865578582</v>
       </c>
       <c r="U5" t="n">
-        <v>4.18144004573043</v>
+        <v>4.181440045729932</v>
       </c>
       <c r="V5" t="n">
-        <v>4.181440045730512</v>
+        <v>4.181440045729329</v>
       </c>
       <c r="W5" t="n">
-        <v>2.690133029619891</v>
+        <v>2.69013302961917</v>
       </c>
       <c r="X5" t="n">
-        <v>2.690133029619804</v>
+        <v>2.690133029619029</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.479763630922297</v>
+        <v>3.479763630921958</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.479763630922298</v>
+        <v>3.479763630921562</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1573,22 +1573,22 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0102564302550181</v>
+        <v>0.01025643025501735</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.01025643025501766</v>
+        <v>0.01025643025501708</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.009884808647926655</v>
+        <v>0.009884808647925734</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.009884808647926223</v>
+        <v>0.009884808647925611</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0104444083628621</v>
+        <v>0.01044440836286135</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01044440836286166</v>
+        <v>0.01044440836286108</v>
       </c>
     </row>
     <row r="6">
@@ -1607,7 +1607,7 @@
         <v>2.45980104308333</v>
       </c>
       <c r="E6" t="n">
-        <v>2.575307142304503</v>
+        <v>2.575307142304504</v>
       </c>
       <c r="F6" t="n">
         <v>2.575307142304502</v>
@@ -1619,7 +1619,7 @@
         <v>2.546332895381917</v>
       </c>
       <c r="I6" t="n">
-        <v>462.8226583969786</v>
+        <v>462.8226583969787</v>
       </c>
       <c r="J6" t="n">
         <v>462.8226583969372</v>
@@ -1655,19 +1655,19 @@
         <v>0.2146792877065669</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9520470525262248</v>
+        <v>0.952047052526225</v>
       </c>
       <c r="V6" t="n">
         <v>0.952047052526121</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9298334427391807</v>
+        <v>0.9298334427391808</v>
       </c>
       <c r="X6" t="n">
         <v>0.9298334427389773</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9760940509823315</v>
+        <v>0.9760940509823317</v>
       </c>
       <c r="Z6" t="n">
         <v>0.976094050982228</v>
@@ -1719,76 +1719,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.345789062664506</v>
+        <v>2.345789062664478</v>
       </c>
       <c r="D7" t="n">
-        <v>2.345789062664481</v>
+        <v>2.345789062664485</v>
       </c>
       <c r="E7" t="n">
-        <v>2.326634843410316</v>
+        <v>2.326634843410293</v>
       </c>
       <c r="F7" t="n">
-        <v>2.326634843410295</v>
+        <v>2.3266348434103</v>
       </c>
       <c r="G7" t="n">
-        <v>2.364219089796888</v>
+        <v>2.364219089796864</v>
       </c>
       <c r="H7" t="n">
-        <v>2.364219089796868</v>
+        <v>2.364219089796869</v>
       </c>
       <c r="I7" t="n">
-        <v>684.9000076077568</v>
+        <v>684.9000076076563</v>
       </c>
       <c r="J7" t="n">
-        <v>684.9000076076752</v>
+        <v>684.9000076076826</v>
       </c>
       <c r="K7" t="n">
-        <v>545.5513858680839</v>
+        <v>545.5513858679956</v>
       </c>
       <c r="L7" t="n">
-        <v>545.5513858680039</v>
+        <v>545.5513858680213</v>
       </c>
       <c r="M7" t="n">
-        <v>696.0684395496039</v>
+        <v>696.0684395495034</v>
       </c>
       <c r="N7" t="n">
-        <v>696.0684395495222</v>
+        <v>696.0684395495296</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2216070221405304</v>
+        <v>0.2216070221405289</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2216070221405297</v>
+        <v>0.221607022140529</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2230321082553361</v>
+        <v>0.2230321082553342</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2230321082553343</v>
+        <v>0.2230321082553347</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2262018639746856</v>
+        <v>0.2262018639746835</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2262018639746838</v>
+        <v>0.226201863974684</v>
       </c>
       <c r="U7" t="n">
-        <v>3.321360497066971</v>
+        <v>3.321360497066342</v>
       </c>
       <c r="V7" t="n">
-        <v>3.321360497066411</v>
+        <v>3.321360497066525</v>
       </c>
       <c r="W7" t="n">
-        <v>1.933417175669148</v>
+        <v>1.933417175668677</v>
       </c>
       <c r="X7" t="n">
-        <v>1.933417175668684</v>
+        <v>1.933417175668826</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.338619877407671</v>
+        <v>3.338619877407057</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.338619877407135</v>
+        <v>3.338619877407233</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1809,22 +1809,22 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0246764636409993</v>
+        <v>0.02467646364099519</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.02467646364099569</v>
+        <v>0.02467646364099637</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.01900975023442091</v>
+        <v>0.0190097502344173</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01900975023441744</v>
+        <v>0.01900975023441841</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.02495601381400573</v>
+        <v>0.02495601381400163</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02495601381400212</v>
+        <v>0.02495601381400281</v>
       </c>
     </row>
     <row r="8">
@@ -1861,7 +1861,7 @@
         <v>490.1490905872779</v>
       </c>
       <c r="K8" t="n">
-        <v>399.8046537772933</v>
+        <v>399.8046537772931</v>
       </c>
       <c r="L8" t="n">
         <v>399.8046537772732</v>
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.03712973997003136</v>
+        <v>0.03712973997003137</v>
       </c>
       <c r="AH8" t="n">
         <v>0.0371297399700309</v>
@@ -1955,76 +1955,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.231587047854692</v>
+        <v>1.231587047769074</v>
       </c>
       <c r="D9" t="n">
-        <v>1.231587047854708</v>
+        <v>1.231587047769073</v>
       </c>
       <c r="E9" t="n">
-        <v>1.235926748212021</v>
+        <v>1.235926748147279</v>
       </c>
       <c r="F9" t="n">
-        <v>1.235926748212036</v>
+        <v>1.235926748147278</v>
       </c>
       <c r="G9" t="n">
-        <v>1.240978847230464</v>
+        <v>1.240978847151445</v>
       </c>
       <c r="H9" t="n">
-        <v>1.240978847230479</v>
+        <v>1.240978847151442</v>
       </c>
       <c r="I9" t="n">
-        <v>815.8280364100059</v>
+        <v>815.8280353694297</v>
       </c>
       <c r="J9" t="n">
-        <v>815.8280364102174</v>
+        <v>815.8280353694066</v>
       </c>
       <c r="K9" t="n">
-        <v>758.2090790506487</v>
+        <v>758.20907819808</v>
       </c>
       <c r="L9" t="n">
-        <v>758.2090790508603</v>
+        <v>758.2090781980856</v>
       </c>
       <c r="M9" t="n">
-        <v>824.7385005737856</v>
+        <v>824.7384995332095</v>
       </c>
       <c r="N9" t="n">
-        <v>824.7385005739969</v>
+        <v>824.7384995331862</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01990546858487345</v>
+        <v>0.01990546857828753</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01990546858487479</v>
+        <v>0.01990546857828738</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01948707957508305</v>
+        <v>0.01948707956990367</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01948707957508431</v>
+        <v>0.01948707956990369</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01989124749655848</v>
+        <v>0.01989124749023696</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01989124749655975</v>
+        <v>0.01989124749023679</v>
       </c>
       <c r="U9" t="n">
-        <v>5.013696588365936</v>
+        <v>5.013696583960182</v>
       </c>
       <c r="V9" t="n">
-        <v>5.013696588367762</v>
+        <v>5.013696583960192</v>
       </c>
       <c r="W9" t="n">
-        <v>3.38468643062121</v>
+        <v>3.384686427096209</v>
       </c>
       <c r="X9" t="n">
-        <v>3.384686430622946</v>
+        <v>3.384686427096627</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.568400569645822</v>
+        <v>4.568400564985925</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.568400569647335</v>
+        <v>4.56840056498585</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -2045,22 +2045,22 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.01347319579546987</v>
+        <v>0.01347319577844026</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.01347319579547339</v>
+        <v>0.01347319577843989</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0125177222061523</v>
+        <v>0.01251772219219954</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01251772220615583</v>
+        <v>0.01251772219219965</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01361822540557363</v>
+        <v>0.01361822538854402</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01361822540557715</v>
+        <v>0.01361822538854365</v>
       </c>
     </row>
     <row r="10">
@@ -2191,76 +2191,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.401640859356139</v>
+        <v>2.401640859208354</v>
       </c>
       <c r="D11" t="n">
-        <v>2.40164085935612</v>
+        <v>2.401640859208391</v>
       </c>
       <c r="E11" t="n">
-        <v>2.354305633160197</v>
+        <v>2.354305633061668</v>
       </c>
       <c r="F11" t="n">
-        <v>2.354305633160181</v>
+        <v>2.354305633061694</v>
       </c>
       <c r="G11" t="n">
-        <v>2.412504918955086</v>
+        <v>2.412504918802183</v>
       </c>
       <c r="H11" t="n">
-        <v>2.412504918955066</v>
+        <v>2.412504918802216</v>
       </c>
       <c r="I11" t="n">
-        <v>914.1099784461629</v>
+        <v>914.1099778396826</v>
       </c>
       <c r="J11" t="n">
-        <v>914.1099784460888</v>
+        <v>914.1099778398153</v>
       </c>
       <c r="K11" t="n">
-        <v>691.8811635331762</v>
+        <v>691.8811631423655</v>
       </c>
       <c r="L11" t="n">
-        <v>691.8811635331159</v>
+        <v>691.8811631424701</v>
       </c>
       <c r="M11" t="n">
-        <v>922.7266910441036</v>
+        <v>922.7266904376233</v>
       </c>
       <c r="N11" t="n">
-        <v>922.7266910440293</v>
+        <v>922.726690437756</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2281351542213724</v>
+        <v>0.2281351542041002</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2281351542213706</v>
+        <v>0.2281351542041025</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.225236818151744</v>
+        <v>0.2252368181434342</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2252368181517426</v>
+        <v>0.2252368181434364</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2301451916525176</v>
+        <v>0.2301451916396223</v>
       </c>
       <c r="T11" t="n">
-        <v>0.230145191652516</v>
+        <v>0.2301451916396251</v>
       </c>
       <c r="U11" t="n">
-        <v>4.497874967636145</v>
+        <v>4.497874964523046</v>
       </c>
       <c r="V11" t="n">
-        <v>4.497874967635738</v>
+        <v>4.497874964523856</v>
       </c>
       <c r="W11" t="n">
-        <v>2.557134138059788</v>
+        <v>2.557134136480725</v>
       </c>
       <c r="X11" t="n">
-        <v>2.557134138059487</v>
+        <v>2.557134136481259</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.632064213363097</v>
+        <v>4.632064210096298</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.632064213362678</v>
+        <v>4.632064210097116</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2281,22 +2281,22 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.03259013181615185</v>
+        <v>0.03259013179521211</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.03259013181614914</v>
+        <v>0.0325901317952174</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0240595251764346</v>
+        <v>0.02405952516294109</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.02405952517643234</v>
+        <v>0.02405952516294529</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.03280581146662055</v>
+        <v>0.0328058114456808</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03280581146661784</v>
+        <v>0.0328058114456861</v>
       </c>
     </row>
     <row r="12">
@@ -2405,13 +2405,13 @@
         <v>0.03636073231494269</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.03442866310285014</v>
+        <v>0.03442866310285013</v>
       </c>
       <c r="AJ12" t="n">
         <v>0.03442866310284985</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.03613142002858127</v>
+        <v>0.03613142002858126</v>
       </c>
       <c r="AL12" t="n">
         <v>0.0361314200285808</v>
@@ -2427,76 +2427,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.209859455960509</v>
+        <v>1.209859455959315</v>
       </c>
       <c r="D13" t="n">
-        <v>1.209859455960507</v>
+        <v>1.209859455959314</v>
       </c>
       <c r="E13" t="n">
-        <v>1.193107555204878</v>
+        <v>1.193107555203807</v>
       </c>
       <c r="F13" t="n">
-        <v>1.193107555204873</v>
+        <v>1.193107555203805</v>
       </c>
       <c r="G13" t="n">
-        <v>1.199751393988662</v>
+        <v>1.199751393987417</v>
       </c>
       <c r="H13" t="n">
-        <v>1.199751393988657</v>
+        <v>1.199751393987414</v>
       </c>
       <c r="I13" t="n">
-        <v>551.7542272345692</v>
+        <v>551.7542272200436</v>
       </c>
       <c r="J13" t="n">
-        <v>551.7542272345349</v>
+        <v>551.7542272200184</v>
       </c>
       <c r="K13" t="n">
-        <v>459.1305455656839</v>
+        <v>459.130545553183</v>
       </c>
       <c r="L13" t="n">
-        <v>459.1305455656374</v>
+        <v>459.1305455531694</v>
       </c>
       <c r="M13" t="n">
-        <v>536.6677608963153</v>
+        <v>536.6677608817897</v>
       </c>
       <c r="N13" t="n">
-        <v>536.6677608962809</v>
+        <v>536.6677608817644</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0182341153622441</v>
+        <v>0.01823411536215217</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01823411536224389</v>
+        <v>0.01823411536215202</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01771776306212235</v>
+        <v>0.01771776306203666</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01771776306212201</v>
+        <v>0.01771776306203655</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01824927016482503</v>
+        <v>0.01824927016472546</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01824927016482478</v>
+        <v>0.01824927016472527</v>
       </c>
       <c r="U13" t="n">
-        <v>3.895561282427561</v>
+        <v>3.89556128236514</v>
       </c>
       <c r="V13" t="n">
-        <v>3.895561282427357</v>
+        <v>3.89556128236449</v>
       </c>
       <c r="W13" t="n">
-        <v>1.602827862214278</v>
+        <v>1.60282786217157</v>
       </c>
       <c r="X13" t="n">
-        <v>1.602827862213756</v>
+        <v>1.602827862171448</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.183778641457233</v>
+        <v>3.18377864137998</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.183778641457023</v>
+        <v>3.183778641379583</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2517,22 +2517,22 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.009151476544916409</v>
+        <v>0.009151476544678629</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.009151476544915844</v>
+        <v>0.009151476544678178</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.007608721141722933</v>
+        <v>0.007608721141518298</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.007608721141722161</v>
+        <v>0.007608721141518044</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.008905924316585314</v>
+        <v>0.008905924316347532</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.008905924316584747</v>
+        <v>0.00890592431634708</v>
       </c>
     </row>
     <row r="14">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.410241413919384</v>
+        <v>2.410241413919385</v>
       </c>
       <c r="D15" t="n">
         <v>2.410241413919331</v>
@@ -2711,7 +2711,7 @@
         <v>0.209851916968826</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2035436216765866</v>
+        <v>0.2035436216765865</v>
       </c>
       <c r="T15" t="n">
         <v>0.2035436216765855</v>
@@ -2781,76 +2781,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.369366794343237</v>
+        <v>1.341212437336297</v>
       </c>
       <c r="D16" t="n">
-        <v>1.369366794259893</v>
+        <v>1.341212437336329</v>
       </c>
       <c r="E16" t="n">
-        <v>1.519482643490708</v>
+        <v>1.479705081167416</v>
       </c>
       <c r="F16" t="n">
-        <v>1.519482643373014</v>
+        <v>1.479705081167424</v>
       </c>
       <c r="G16" t="n">
-        <v>1.154442898835607</v>
+        <v>1.114410334624249</v>
       </c>
       <c r="H16" t="n">
-        <v>1.154442898717152</v>
+        <v>1.114410334624251</v>
       </c>
       <c r="I16" t="n">
-        <v>435.0134425291626</v>
+        <v>445.312118147967</v>
       </c>
       <c r="J16" t="n">
-        <v>435.0134425595875</v>
+        <v>445.3121181480039</v>
       </c>
       <c r="K16" t="n">
-        <v>318.1353225432958</v>
+        <v>331.9456072546465</v>
       </c>
       <c r="L16" t="n">
-        <v>318.1353225840994</v>
+        <v>331.945607254687</v>
       </c>
       <c r="M16" t="n">
-        <v>420.3891426172511</v>
+        <v>431.2234164788381</v>
       </c>
       <c r="N16" t="n">
-        <v>420.3891426492606</v>
+        <v>431.2234164788749</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0187383382811975</v>
+        <v>0.01838410030746193</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01873833828014877</v>
+        <v>0.0183841003074624</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.02075931199346882</v>
+        <v>0.02033669968530184</v>
       </c>
       <c r="R16" t="n">
-        <v>0.02075931199221805</v>
+        <v>0.02033669968530218</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01700583638973179</v>
+        <v>0.0165628239305196</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01700583638842065</v>
+        <v>0.01656282393051984</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9854274618802966</v>
+        <v>1.021969356141318</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9854274619882872</v>
+        <v>1.02196935614142</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4706959536289703</v>
+        <v>0.5124812175232898</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4706959537524571</v>
+        <v>0.512481217523389</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.8078310965163508</v>
+        <v>0.8395391510193317</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.8078310966100591</v>
+        <v>0.8395391510194179</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2871,22 +2871,22 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.03617872749760378</v>
+        <v>0.03636072401972167</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.03617872749814146</v>
+        <v>0.0363607240197223</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.03418690352033271</v>
+        <v>0.03442866030632046</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.03418690352104702</v>
+        <v>0.03442866030632116</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.03594069764020458</v>
+        <v>0.03613141173335978</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.03594069764076806</v>
+        <v>0.03613141173336042</v>
       </c>
     </row>
     <row r="17">
@@ -2897,76 +2897,76 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>22.44232213988976</v>
+        <v>22.41416778264819</v>
       </c>
       <c r="D17" t="n">
-        <v>22.44232213980615</v>
+        <v>22.41416778264804</v>
       </c>
       <c r="E17" t="n">
-        <v>23.69103872425993</v>
+        <v>23.65126116177226</v>
       </c>
       <c r="F17" t="n">
-        <v>23.69097274229499</v>
+        <v>23.65119517992509</v>
       </c>
       <c r="G17" t="n">
-        <v>21.98880331149084</v>
+        <v>21.94877074704628</v>
       </c>
       <c r="H17" t="n">
-        <v>21.98880331137216</v>
+        <v>21.94877074704612</v>
       </c>
       <c r="I17" t="n">
-        <v>7692.653142982975</v>
+        <v>7702.951816940053</v>
       </c>
       <c r="J17" t="n">
-        <v>7692.653143013189</v>
+        <v>7702.95181693998</v>
       </c>
       <c r="K17" t="n">
-        <v>5995.493517858697</v>
+        <v>6009.303801314025</v>
       </c>
       <c r="L17" t="n">
-        <v>5995.484617713478</v>
+        <v>6009.294901128162</v>
       </c>
       <c r="M17" t="n">
-        <v>7698.001202660278</v>
+        <v>7708.835474860139</v>
       </c>
       <c r="N17" t="n">
-        <v>7698.001202692075</v>
+        <v>7708.835474860065</v>
       </c>
       <c r="O17" t="n">
-        <v>1.228176479876839</v>
+        <v>1.227822241879152</v>
       </c>
       <c r="P17" t="n">
-        <v>1.228176479875784</v>
+        <v>1.227822241879149</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.254676962839943</v>
+        <v>1.2542543505182</v>
       </c>
       <c r="R17" t="n">
-        <v>1.254676078199959</v>
+        <v>1.254253465879471</v>
       </c>
       <c r="S17" t="n">
-        <v>1.237919806197084</v>
+        <v>1.237476793718553</v>
       </c>
       <c r="T17" t="n">
-        <v>1.237919806195764</v>
+        <v>1.23747679371855</v>
       </c>
       <c r="U17" t="n">
-        <v>31.80434781341469</v>
+        <v>31.84088970009331</v>
       </c>
       <c r="V17" t="n">
-        <v>31.80434781352288</v>
+        <v>31.84088970009263</v>
       </c>
       <c r="W17" t="n">
-        <v>17.41922260484354</v>
+        <v>17.4610078635899</v>
       </c>
       <c r="X17" t="n">
-        <v>17.41921199106084</v>
+        <v>17.46099724968429</v>
       </c>
       <c r="Y17" t="n">
-        <v>30.02429320233029</v>
+        <v>30.05600124882837</v>
       </c>
       <c r="Z17" t="n">
-        <v>30.02429320242384</v>
+        <v>30.05600124882807</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2987,22 +2987,22 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.3215592737398031</v>
+        <v>0.321741270223709</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.3215592737403333</v>
+        <v>0.3217412702237114</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.2850278100415673</v>
+        <v>0.2852695667998996</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.2850276643856322</v>
+        <v>0.2852694211432593</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.3218622643385006</v>
+        <v>0.3220529783934438</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.3218622643390567</v>
+        <v>0.3220529783934462</v>
       </c>
     </row>
   </sheetData>
@@ -3098,13 +3098,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.947581187572458</v>
+        <v>3.947581187571988</v>
       </c>
       <c r="D4" t="n">
-        <v>3.947577293964593</v>
+        <v>3.947577293963478</v>
       </c>
       <c r="E4" t="n">
-        <v>4.18144004573043</v>
+        <v>4.181440045729932</v>
       </c>
       <c r="F4" t="n">
         <v>0.9440721723615862</v>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9520470525262248</v>
+        <v>0.952047052526225</v>
       </c>
       <c r="D5" t="n">
         <v>0.952047052526121</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9520470525262248</v>
+        <v>0.952047052526225</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -3142,16 +3142,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.135300417386442</v>
+        <v>3.135300417385851</v>
       </c>
       <c r="D6" t="n">
-        <v>3.135297382033751</v>
+        <v>3.135297382033858</v>
       </c>
       <c r="E6" t="n">
-        <v>3.321360497066971</v>
+        <v>3.321360497066342</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9439807633513934</v>
+        <v>0.943980763351394</v>
       </c>
     </row>
     <row r="7">
@@ -3186,16 +3186,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.936338588785695</v>
+        <v>4.936338584451514</v>
       </c>
       <c r="D8" t="n">
-        <v>4.936334279939866</v>
+        <v>4.936334275603902</v>
       </c>
       <c r="E8" t="n">
-        <v>5.013696588365936</v>
+        <v>5.013696583960182</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9845706659314513</v>
+        <v>0.9845706659321684</v>
       </c>
     </row>
     <row r="9">
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.427972646172244</v>
+        <v>4.427972643109716</v>
       </c>
       <c r="D10" t="n">
-        <v>4.427968626776122</v>
+        <v>4.427968623714794</v>
       </c>
       <c r="E10" t="n">
-        <v>4.497874967636145</v>
+        <v>4.497874964523046</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9844588117795907</v>
+        <v>0.9844588117800775</v>
       </c>
     </row>
     <row r="11">
@@ -3274,16 +3274,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.605110513282043</v>
+        <v>3.605110513224597</v>
       </c>
       <c r="D12" t="n">
-        <v>3.605099476216389</v>
+        <v>3.605099476158533</v>
       </c>
       <c r="E12" t="n">
-        <v>3.895561282427561</v>
+        <v>3.89556128236514</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9254405853000673</v>
+        <v>0.9254405853001498</v>
       </c>
     </row>
     <row r="13">
@@ -3340,13 +3340,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9854274618802966</v>
+        <v>1.021969356141318</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9854274619882872</v>
+        <v>1.02196935614142</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9854274618802966</v>
+        <v>1.021969356141318</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -3591,40 +3591,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.054028754711721</v>
+        <v>5.054028754711718</v>
       </c>
       <c r="C4" t="n">
-        <v>5.437107406865591</v>
+        <v>5.437107406865588</v>
       </c>
       <c r="D4" t="n">
-        <v>5.208401435619603</v>
+        <v>5.208401435619599</v>
       </c>
       <c r="E4" t="n">
-        <v>1572.242933770347</v>
+        <v>1572.242933770302</v>
       </c>
       <c r="F4" t="n">
-        <v>1464.487332618474</v>
+        <v>1464.487332618419</v>
       </c>
       <c r="G4" t="n">
-        <v>1605.072407822268</v>
+        <v>1605.072407822223</v>
       </c>
       <c r="H4" t="n">
-        <v>0.246754201190682</v>
+        <v>0.2467542011906818</v>
       </c>
       <c r="I4" t="n">
-        <v>0.258807309215663</v>
+        <v>0.2588073092156627</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2530883265058977</v>
+        <v>0.2530883265058974</v>
       </c>
       <c r="K4" t="n">
-        <v>6.279609463525886</v>
+        <v>6.279609463525389</v>
       </c>
       <c r="L4" t="n">
-        <v>4.425848836511372</v>
+        <v>4.425848836510652</v>
       </c>
       <c r="M4" t="n">
-        <v>5.640548994127261</v>
+        <v>5.640548994126923</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -3636,13 +3636,13 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.07092826674974223</v>
+        <v>0.07092826674974148</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06914800496101894</v>
+        <v>0.06914800496101803</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07155448335404917</v>
+        <v>0.07155448335404842</v>
       </c>
     </row>
     <row r="5">
@@ -3652,40 +3652,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.345789062664506</v>
+        <v>2.345789062664478</v>
       </c>
       <c r="C5" t="n">
-        <v>2.326634843410316</v>
+        <v>2.326634843410293</v>
       </c>
       <c r="D5" t="n">
-        <v>2.364219089796888</v>
+        <v>2.364219089796864</v>
       </c>
       <c r="E5" t="n">
-        <v>684.9000076077568</v>
+        <v>684.9000076076563</v>
       </c>
       <c r="F5" t="n">
-        <v>545.5513858680839</v>
+        <v>545.5513858679956</v>
       </c>
       <c r="G5" t="n">
-        <v>696.0684395496039</v>
+        <v>696.0684395495034</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2216070221405304</v>
+        <v>0.2216070221405289</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2230321082553361</v>
+        <v>0.2230321082553342</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2262018639746856</v>
+        <v>0.2262018639746835</v>
       </c>
       <c r="K5" t="n">
-        <v>3.321360497066971</v>
+        <v>3.321360497066342</v>
       </c>
       <c r="L5" t="n">
-        <v>1.933417175669148</v>
+        <v>1.933417175668677</v>
       </c>
       <c r="M5" t="n">
-        <v>3.338619877407671</v>
+        <v>3.338619877407057</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -3697,13 +3697,13 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0246764636409993</v>
+        <v>0.02467646364099519</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01900975023442091</v>
+        <v>0.0190097502344173</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02495601381400573</v>
+        <v>0.02495601381400163</v>
       </c>
     </row>
     <row r="6">
@@ -3713,40 +3713,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.610400110812586</v>
+        <v>2.610400110726969</v>
       </c>
       <c r="C6" t="n">
-        <v>2.860953057205503</v>
+        <v>2.860953057140761</v>
       </c>
       <c r="D6" t="n">
-        <v>2.658939057905296</v>
+        <v>2.658939057826277</v>
       </c>
       <c r="E6" t="n">
-        <v>1305.977126997311</v>
+        <v>1305.977125956735</v>
       </c>
       <c r="F6" t="n">
-        <v>1158.013732827942</v>
+        <v>1158.013731975373</v>
       </c>
       <c r="G6" t="n">
-        <v>1323.208749245581</v>
+        <v>1323.208748205005</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03885712550549156</v>
+        <v>0.03885712549890564</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04178257970185242</v>
+        <v>0.04178257969667305</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03938003826617407</v>
+        <v>0.03938003825985255</v>
       </c>
       <c r="K6" t="n">
-        <v>6.159818953635167</v>
+        <v>6.159818949229413</v>
       </c>
       <c r="L6" t="n">
-        <v>4.185162422491213</v>
+        <v>4.185162418966212</v>
       </c>
       <c r="M6" t="n">
-        <v>5.767737523207854</v>
+        <v>5.767737518547957</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -3758,13 +3758,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05060293576550123</v>
+        <v>0.05060293574847163</v>
       </c>
       <c r="R6" t="n">
-        <v>0.04809064894259394</v>
+        <v>0.04809064892864118</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05088340324847261</v>
+        <v>0.05088340323144301</v>
       </c>
     </row>
     <row r="7">
@@ -3774,40 +3774,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.861441902439521</v>
+        <v>4.861441902291737</v>
       </c>
       <c r="C7" t="n">
-        <v>4.917271959867128</v>
+        <v>4.9172719597686</v>
       </c>
       <c r="D7" t="n">
-        <v>4.936968917893775</v>
+        <v>4.936968917740872</v>
       </c>
       <c r="E7" t="n">
-        <v>1376.932636843142</v>
+        <v>1376.932636236661</v>
       </c>
       <c r="F7" t="n">
-        <v>1146.946139274106</v>
+        <v>1146.946138883296</v>
       </c>
       <c r="G7" t="n">
-        <v>1393.646452310169</v>
+        <v>1393.646451703689</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4372762606130435</v>
+        <v>0.4372762605957713</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4420487266682223</v>
+        <v>0.4420487266599126</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4432745049319249</v>
+        <v>0.4432745049190295</v>
       </c>
       <c r="K7" t="n">
-        <v>5.44992202016237</v>
+        <v>5.449922017049271</v>
       </c>
       <c r="L7" t="n">
-        <v>3.480744966224032</v>
+        <v>3.480744964644968</v>
       </c>
       <c r="M7" t="n">
-        <v>5.621930611496197</v>
+        <v>5.621930608229398</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -3819,13 +3819,13 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.05613222834084461</v>
+        <v>0.05613222831990487</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04751639043431692</v>
+        <v>0.04751639042082341</v>
       </c>
       <c r="S7" t="n">
-        <v>0.05655058160921153</v>
+        <v>0.05655058158827178</v>
       </c>
     </row>
     <row r="8">
@@ -3835,40 +3835,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.551072298887246</v>
+        <v>2.551072298886052</v>
       </c>
       <c r="C8" t="n">
-        <v>2.672813845147754</v>
+        <v>2.672813845146683</v>
       </c>
       <c r="D8" t="n">
-        <v>2.314161770054634</v>
+        <v>2.314161770053389</v>
       </c>
       <c r="E8" t="n">
-        <v>997.0668290300034</v>
+        <v>997.0668290154779</v>
       </c>
       <c r="F8" t="n">
-        <v>791.0763158701654</v>
+        <v>791.0763158576647</v>
       </c>
       <c r="G8" t="n">
-        <v>967.8916610226206</v>
+        <v>967.8916610080951</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03661822179182588</v>
+        <v>0.03661822179173395</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03805447895384531</v>
+        <v>0.03805447895375963</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03481209741068246</v>
+        <v>0.0348120974105829</v>
       </c>
       <c r="K8" t="n">
-        <v>4.917531977782594</v>
+        <v>4.917531977720173</v>
       </c>
       <c r="L8" t="n">
-        <v>2.115309274182514</v>
+        <v>2.115309274139806</v>
       </c>
       <c r="M8" t="n">
-        <v>4.02331892337509</v>
+        <v>4.023318923297837</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3880,13 +3880,13 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.04551220885985956</v>
+        <v>0.04551220885962178</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04203738424457307</v>
+        <v>0.04203738424436843</v>
       </c>
       <c r="S8" t="n">
-        <v>0.04503734434516658</v>
+        <v>0.04503734434492879</v>
       </c>
     </row>
     <row r="9">
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.65022321603094</v>
+        <v>3.650223216030941</v>
       </c>
       <c r="C9" t="n">
         <v>3.956774968272925</v>
@@ -3957,40 +3957,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.369366794343237</v>
+        <v>1.341212437336297</v>
       </c>
       <c r="C10" t="n">
-        <v>1.519482643490708</v>
+        <v>1.479705081167416</v>
       </c>
       <c r="D10" t="n">
-        <v>1.154442898835607</v>
+        <v>1.114410334624249</v>
       </c>
       <c r="E10" t="n">
-        <v>435.0134425291626</v>
+        <v>445.312118147967</v>
       </c>
       <c r="F10" t="n">
-        <v>318.1353225432958</v>
+        <v>331.9456072546465</v>
       </c>
       <c r="G10" t="n">
-        <v>420.3891426172511</v>
+        <v>431.2234164788381</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0187383382811975</v>
+        <v>0.01838410030746193</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02075931199346882</v>
+        <v>0.02033669968530184</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01700583638973179</v>
+        <v>0.0165628239305196</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9854274618802966</v>
+        <v>1.021969356141318</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4706959536289703</v>
+        <v>0.5124812175232898</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8078310965163508</v>
+        <v>0.8395391510193317</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -4002,13 +4002,13 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.03617872749760378</v>
+        <v>0.03636072401972167</v>
       </c>
       <c r="R10" t="n">
-        <v>0.03418690352033271</v>
+        <v>0.03442866030632046</v>
       </c>
       <c r="S10" t="n">
-        <v>0.03594069764020458</v>
+        <v>0.03613141173335978</v>
       </c>
     </row>
   </sheetData>

--- a/example/training/training_validation_reference.xlsx
+++ b/example/training/training_validation_reference.xlsx
@@ -863,28 +863,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>3.235629785991629</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3.235629785991599</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2.524211865098793</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2.524208126570088</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3.238101220224796</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3.238101220224764</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3.235629785991629</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3.235629785991599</v>
       </c>
     </row>
     <row r="8">
@@ -1437,22 +1437,22 @@
         <v>1.184691312222558</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>0.2058874357221409</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>0.2058874357221295</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>0.1703726110053254</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>0.1703726110053168</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>0.2104178301089004</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>0.2104178301088888</v>
       </c>
       <c r="AG4" t="n">
         <v>0.03712973997003137</v>
@@ -1555,22 +1555,22 @@
         <v>3.479763630921562</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>0.2601252531131549</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>0.2601252531131489</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>0.250867393101304</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>0.2508673931013017</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>0.2649764909361988</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.2649764909361928</v>
       </c>
       <c r="AG5" t="n">
         <v>0.01025643025501735</v>
@@ -1673,22 +1673,22 @@
         <v>0.976094050982228</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>0.194408950585384</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>0.1944089505853666</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>0.1939188268504544</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>0.1939188268504283</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>0.1988173597292384</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.198817359729221</v>
       </c>
       <c r="AG6" t="n">
         <v>0.02354209652469276</v>
@@ -1791,22 +1791,22 @@
         <v>3.338619877407233</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>0.2876926816766135</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>0.2876926816766245</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>0.2291592049195388</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>0.2291592049195496</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>0.2923839885824142</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>0.2923839885824251</v>
       </c>
       <c r="AG7" t="n">
         <v>0.02467646364099519</v>
@@ -1909,22 +1909,22 @@
         <v>1.199336953561955</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>0.2058874357221409</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>0.2058874357221295</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>0.1679381978600721</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>0.1679381978600637</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>0.209382743442087</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.2093827434420754</v>
       </c>
       <c r="AG8" t="n">
         <v>0.03712973997003137</v>
@@ -2027,22 +2027,22 @@
         <v>4.56840056498585</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>0.3426890826037868</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>0.3426890826037771</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>0.318486203176267</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>0.3184862031762692</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>0.3464319287153168</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>0.346431928715307</v>
       </c>
       <c r="AG9" t="n">
         <v>0.01347319577844026</v>
@@ -2145,22 +2145,22 @@
         <v>0.989866398132994</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>0.194408950585384</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>0.1944089505853666</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>0.1911503310757851</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>0.1911503310757594</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>0.1978101437702927</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>0.1978101437702753</v>
       </c>
       <c r="AG10" t="n">
         <v>0.02354209652469276</v>
@@ -2263,22 +2263,22 @@
         <v>4.632064210097116</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>0.3839724747421777</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>0.3839724747422334</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>0.290625120477421</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>0.290625120477465</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>0.3875919303225582</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.3875919303226139</v>
       </c>
       <c r="AG11" t="n">
         <v>0.03259013179521211</v>
@@ -2381,22 +2381,22 @@
         <v>0.839540281917793</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>0.187053840227591</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>0.1870538402275796</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>0.1394340309086572</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>0.1394340309086499</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>0.1811358721745737</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>0.1811358721745622</v>
       </c>
       <c r="AG12" t="n">
         <v>0.03636073231494315</v>
@@ -2499,22 +2499,22 @@
         <v>3.183778641379583</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>0.2317647123553155</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>0.2317647123553049</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>0.1928580762485674</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>0.1928580762485617</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>0.2254276326215356</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>0.2254276326215249</v>
       </c>
       <c r="AG13" t="n">
         <v>0.009151476544678629</v>
@@ -2617,22 +2617,22 @@
         <v>4.109231807499004</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>0.3766404281076396</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>0.3766404281076396</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>0.08596012856371707</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>0.08595639003504445</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>0.3703033483738596</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>0.3703033483738595</v>
       </c>
       <c r="AG14" t="n">
         <v>0.01469376702111024</v>
@@ -2735,22 +2735,22 @@
         <v>0.7150743687007772</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>0.178044903479134</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>0.1780449034791166</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>0.1540077784922124</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>0.1540077784921901</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>0.1722862824296712</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.1722862824296538</v>
       </c>
       <c r="AG15" t="n">
         <v>0.02283467586414214</v>
@@ -2853,22 +2853,22 @@
         <v>0.8395391510194179</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>0.1870536370711663</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>0.1870536370711818</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>0.1394339624194708</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>0.1394339624194878</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>0.1811356690181489</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.1811356690181644</v>
       </c>
       <c r="AG16" t="n">
         <v>0.03636072401972167</v>
@@ -2969,22 +2969,22 @@
         <v>30.05600124882807</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.235629785991629</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.235629785991599</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.524211865098793</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.524208126570088</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>3.238101220224796</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>3.238101220224764</v>
       </c>
       <c r="AG17" t="n">
         <v>0.321741270223709</v>
@@ -3627,13 +3627,13 @@
         <v>5.640548994126923</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.6604216394206798</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.6151588309570839</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.6742116807743376</v>
       </c>
       <c r="Q4" t="n">
         <v>0.07092826674974148</v>
@@ -3688,13 +3688,13 @@
         <v>3.338619877407057</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.2876926816766135</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.2291592049195388</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.2923839885824142</v>
       </c>
       <c r="Q5" t="n">
         <v>0.02467646364099519</v>
@@ -3749,13 +3749,13 @@
         <v>5.767737518547957</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.5485765183259277</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.4864244010363391</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5558146721574038</v>
       </c>
       <c r="Q6" t="n">
         <v>0.05060293574847163</v>
@@ -3810,13 +3810,13 @@
         <v>5.621930608229398</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.5783814253275616</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.4817754515532061</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5854020740928509</v>
       </c>
       <c r="Q7" t="n">
         <v>0.05613222831990487</v>
@@ -3871,13 +3871,13 @@
         <v>4.023318923297837</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.4188185525829066</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.3322921071572246</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.4065635047961093</v>
       </c>
       <c r="Q8" t="n">
         <v>0.04551220885962178</v>
@@ -3932,13 +3932,13 @@
         <v>4.824306176199871</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.5546853315867736</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.2399679070559295</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.5425896308035308</v>
       </c>
       <c r="Q9" t="n">
         <v>0.03752844288525238</v>
@@ -3993,13 +3993,13 @@
         <v>0.8395391510193317</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.1870536370711663</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.1394339624194708</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.1811356690181489</v>
       </c>
       <c r="Q10" t="n">
         <v>0.03636072401972167</v>

--- a/example/training/training_validation_reference.xlsx
+++ b/example/training/training_validation_reference.xlsx
@@ -863,28 +863,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.235629785991629</v>
+        <v>1.84856217748681</v>
       </c>
       <c r="C7" t="n">
-        <v>3.235629785991599</v>
+        <v>1.848562177486793</v>
       </c>
       <c r="D7" t="n">
-        <v>2.524211865098793</v>
+        <v>1.442118811610278</v>
       </c>
       <c r="E7" t="n">
-        <v>2.524208126570088</v>
+        <v>1.442116675734661</v>
       </c>
       <c r="F7" t="n">
-        <v>3.238101220224796</v>
+        <v>1.849974143672607</v>
       </c>
       <c r="G7" t="n">
-        <v>3.238101220224764</v>
+        <v>1.849974143672589</v>
       </c>
       <c r="H7" t="n">
-        <v>3.235629785991629</v>
+        <v>1.84856217748681</v>
       </c>
       <c r="I7" t="n">
-        <v>3.235629785991599</v>
+        <v>1.848562177486793</v>
       </c>
     </row>
     <row r="8">
@@ -894,28 +894,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.321741270223709</v>
+        <v>0.3220101515667749</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3217412702237114</v>
+        <v>0.3220101515667775</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2852695667998996</v>
+        <v>0.2854435506979248</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2852694211432593</v>
+        <v>0.2854434050412846</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3220529783934438</v>
+        <v>0.3223218597365097</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3220529783934462</v>
+        <v>0.3223218597365123</v>
       </c>
       <c r="H8" t="n">
-        <v>0.321741270223709</v>
+        <v>0.3220101515667749</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3217412702237114</v>
+        <v>0.3220101515667775</v>
       </c>
     </row>
   </sheetData>
@@ -1437,22 +1437,22 @@
         <v>1.184691312222558</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2058874357221409</v>
+        <v>0.1176264751126509</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2058874357221295</v>
+        <v>0.1176264751126444</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1703726110053254</v>
+        <v>0.09733634118082393</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1703726110053168</v>
+        <v>0.09733634118081905</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2104178301089004</v>
+        <v>0.1202147550662845</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2104178301088888</v>
+        <v>0.120214755066278</v>
       </c>
       <c r="AG4" t="n">
         <v>0.03712973997003137</v>
@@ -1555,22 +1555,22 @@
         <v>3.479763630921562</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2601252531131549</v>
+        <v>0.1486133260350092</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2601252531131489</v>
+        <v>0.1486133260350058</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.250867393101304</v>
+        <v>0.1433241764739354</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.2508673931013017</v>
+        <v>0.1433241764739341</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.2649764909361988</v>
+        <v>0.151384908492464</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2649764909361928</v>
+        <v>0.1513849084924606</v>
       </c>
       <c r="AG5" t="n">
         <v>0.01025643025501735</v>
@@ -1673,22 +1673,22 @@
         <v>0.976094050982228</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.194408950585384</v>
+        <v>0.11106865024328</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1944089505853666</v>
+        <v>0.1110686502432701</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1939188268504544</v>
+        <v>0.1107886354521558</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.1939188268504283</v>
+        <v>0.1107886354521409</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1988173597292384</v>
+        <v>0.1135872382602087</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.198817359729221</v>
+        <v>0.1135872382601988</v>
       </c>
       <c r="AG6" t="n">
         <v>0.02354209652469276</v>
@@ -1791,22 +1791,22 @@
         <v>3.338619877407233</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2876926816766135</v>
+        <v>0.1643629973953133</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2876926816766245</v>
+        <v>0.1643629973953196</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2291592049195388</v>
+        <v>0.1309219740377012</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.2291592049195496</v>
+        <v>0.1309219740377074</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.2923839885824142</v>
+        <v>0.1670432090025223</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2923839885824251</v>
+        <v>0.1670432090025285</v>
       </c>
       <c r="AG7" t="n">
         <v>0.02467646364099519</v>
@@ -1909,22 +1909,22 @@
         <v>1.199336953561955</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.2058874357221409</v>
+        <v>0.1176264751126509</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.2058874357221295</v>
+        <v>0.1176264751126444</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.1679381978600721</v>
+        <v>0.09594552567894701</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.1679381978600637</v>
+        <v>0.09594552567894217</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.209382743442087</v>
+        <v>0.1196233950562562</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.2093827434420754</v>
+        <v>0.1196233950562496</v>
       </c>
       <c r="AG8" t="n">
         <v>0.03712973997003137</v>
@@ -2027,40 +2027,40 @@
         <v>4.56840056498585</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.3426890826037868</v>
+        <v>0.1957832380829283</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3426890826037771</v>
+        <v>0.1957832380829227</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.318486203176267</v>
+        <v>0.1819557823926367</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.3184862031762692</v>
+        <v>0.181955782392638</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.3464319287153168</v>
+        <v>0.197921580296207</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.346431928715307</v>
+        <v>0.1979215802962014</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.01347319577844026</v>
+        <v>0.01347735060089541</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.01347319577843989</v>
+        <v>0.01347735060089504</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.01251772219219954</v>
+        <v>0.01252112637738379</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01251772219219965</v>
+        <v>0.0125211263773839</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01361822538854402</v>
+        <v>0.01362238021099917</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01361822538854365</v>
+        <v>0.0136223802109988</v>
       </c>
     </row>
     <row r="10">
@@ -2145,22 +2145,22 @@
         <v>0.989866398132994</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.194408950585384</v>
+        <v>0.11106865024328</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.1944089505853666</v>
+        <v>0.1110686502432701</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1911503310757851</v>
+        <v>0.1092069537036003</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1911503310757594</v>
+        <v>0.1092069537035856</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1978101437702927</v>
+        <v>0.1130118011894014</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1978101437702753</v>
+        <v>0.1130118011893914</v>
       </c>
       <c r="AG10" t="n">
         <v>0.02354209652469276</v>
@@ -2263,40 +2263,40 @@
         <v>4.632064210097116</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3839724747421777</v>
+        <v>0.2193690381629573</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.3839724747422334</v>
+        <v>0.2193690381629891</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.290625120477421</v>
+        <v>0.1660383421700574</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.290625120477465</v>
+        <v>0.1660383421700826</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.3875919303225582</v>
+        <v>0.221436885577996</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.3875919303226139</v>
+        <v>0.2214368855780278</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.03259013179521211</v>
+        <v>0.03285485831582285</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0325901317952174</v>
+        <v>0.03285485831582838</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.02405952516294109</v>
+        <v>0.02423010487578198</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.02405952516294529</v>
+        <v>0.02423010487578634</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0328058114456808</v>
+        <v>0.03307053796629154</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0328058114456861</v>
+        <v>0.03307053796629708</v>
       </c>
     </row>
     <row r="12">
@@ -2381,22 +2381,22 @@
         <v>0.839540281917793</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.187053840227591</v>
+        <v>0.1068665691283385</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.1870538402275796</v>
+        <v>0.106866569128332</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1394340309086572</v>
+        <v>0.07966068210528497</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1394340309086499</v>
+        <v>0.07966068210528079</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.1811358721745737</v>
+        <v>0.1034855482347413</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1811358721745622</v>
+        <v>0.1034855482347347</v>
       </c>
       <c r="AG12" t="n">
         <v>0.03636073231494315</v>
@@ -2499,22 +2499,22 @@
         <v>3.183778641379583</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2317647123553155</v>
+        <v>0.132410538186724</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.2317647123553049</v>
+        <v>0.132410538186718</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1928580762485674</v>
+        <v>0.1101826132641775</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1928580762485617</v>
+        <v>0.1101826132641742</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.2254276326215356</v>
+        <v>0.1287900727174356</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.2254276326215249</v>
+        <v>0.1287900727174295</v>
       </c>
       <c r="AG13" t="n">
         <v>0.009151476544678629</v>
@@ -2617,22 +2617,22 @@
         <v>4.109231807499004</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.3766404281076396</v>
+        <v>0.2151801336872796</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.3766404281076396</v>
+        <v>0.2151801336872796</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.08596012856371707</v>
+        <v>0.04911026691704524</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.08595639003504445</v>
+        <v>0.04910813104144738</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.3703033483738596</v>
+        <v>0.2115596682179912</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.3703033483738595</v>
+        <v>0.2115596682179911</v>
       </c>
       <c r="AG14" t="n">
         <v>0.01469376702111024</v>
@@ -2735,22 +2735,22 @@
         <v>0.7150743687007772</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.178044903479134</v>
+        <v>0.1017196330342683</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.1780449034791166</v>
+        <v>0.1017196330342584</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1540077784922124</v>
+        <v>0.08798687525749183</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.1540077784921901</v>
+        <v>0.08798687525747903</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.1722862824296712</v>
+        <v>0.09842964939256633</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1722862824296538</v>
+        <v>0.09842964939255643</v>
       </c>
       <c r="AG15" t="n">
         <v>0.02283467586414214</v>
@@ -2853,22 +2853,22 @@
         <v>0.8395391510194179</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.1870536370711663</v>
+        <v>0.1068664530621295</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.1870536370711818</v>
+        <v>0.1068664530621384</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1394339624194708</v>
+        <v>0.07966064297642045</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.1394339624194878</v>
+        <v>0.07966064297643019</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.1811356690181489</v>
+        <v>0.1034854321685323</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1811356690181644</v>
+        <v>0.1034854321685411</v>
       </c>
       <c r="AG16" t="n">
         <v>0.03636072401972167</v>
@@ -2969,40 +2969,40 @@
         <v>30.05600124882807</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.235629785991629</v>
+        <v>1.84856217748681</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.235629785991599</v>
+        <v>1.848562177486793</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.524211865098793</v>
+        <v>1.442118811610278</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.524208126570088</v>
+        <v>1.442116675734661</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.238101220224796</v>
+        <v>1.849974143672607</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.238101220224764</v>
+        <v>1.849974143672589</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.321741270223709</v>
+        <v>0.3220101515667749</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.3217412702237114</v>
+        <v>0.3220101515667775</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.2852695667998996</v>
+        <v>0.2854435506979248</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.2852694211432593</v>
+        <v>0.2854434050412846</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.3220529783934438</v>
+        <v>0.3223218597365097</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.3220529783934462</v>
+        <v>0.3223218597365123</v>
       </c>
     </row>
   </sheetData>
@@ -3627,13 +3627,13 @@
         <v>5.640548994126923</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6604216394206798</v>
+        <v>0.3773084513909402</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6151588309570839</v>
+        <v>0.3514491531069152</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6742116807743376</v>
+        <v>0.3851869018189573</v>
       </c>
       <c r="Q4" t="n">
         <v>0.07092826674974148</v>
@@ -3688,13 +3688,13 @@
         <v>3.338619877407057</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2876926816766135</v>
+        <v>0.1643629973953133</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2291592049195388</v>
+        <v>0.1309219740377012</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2923839885824142</v>
+        <v>0.1670432090025223</v>
       </c>
       <c r="Q5" t="n">
         <v>0.02467646364099519</v>
@@ -3749,22 +3749,22 @@
         <v>5.767737518547957</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5485765183259277</v>
+        <v>0.3134097131955792</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4864244010363391</v>
+        <v>0.2779013080715838</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5558146721574038</v>
+        <v>0.3175449753524632</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05060293574847163</v>
+        <v>0.05060709057092678</v>
       </c>
       <c r="R6" t="n">
-        <v>0.04809064892864118</v>
+        <v>0.04809405311382543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05088340323144301</v>
+        <v>0.05088755805389816</v>
       </c>
     </row>
     <row r="7">
@@ -3810,22 +3810,22 @@
         <v>5.621930608229398</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5783814253275616</v>
+        <v>0.3304376884062373</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4817754515532061</v>
+        <v>0.2752452958736577</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5854020740928509</v>
+        <v>0.3344486867673974</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.05613222831990487</v>
+        <v>0.05639695484051561</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04751639042082341</v>
+        <v>0.0476869701336643</v>
       </c>
       <c r="S7" t="n">
-        <v>0.05655058158827178</v>
+        <v>0.05681530810888252</v>
       </c>
     </row>
     <row r="8">
@@ -3871,13 +3871,13 @@
         <v>4.023318923297837</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4188185525829066</v>
+        <v>0.2392771073150625</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3322921071572246</v>
+        <v>0.1898432953694624</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4065635047961093</v>
+        <v>0.2322756209521769</v>
       </c>
       <c r="Q8" t="n">
         <v>0.04551220885962178</v>
@@ -3932,13 +3932,13 @@
         <v>4.824306176199871</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5546853315867736</v>
+        <v>0.316899766721548</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2399679070559295</v>
+        <v>0.1370971421745371</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5425896308035308</v>
+        <v>0.3099893176105575</v>
       </c>
       <c r="Q9" t="n">
         <v>0.03752844288525238</v>
@@ -3993,13 +3993,13 @@
         <v>0.8395391510193317</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1870536370711663</v>
+        <v>0.1068664530621295</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1394339624194708</v>
+        <v>0.07966064297642045</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1811356690181489</v>
+        <v>0.1034854321685323</v>
       </c>
       <c r="Q10" t="n">
         <v>0.03636072401972167</v>

--- a/example/training/training_validation_reference.xlsx
+++ b/example/training/training_validation_reference.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Made on 2026-10-19 by openalaqs_standalone/validation/tools/regenerate_training_validation_xlsx.py</t>
+          <t>Made on 2026-10-20 by openalaqs_standalone/validation/tools/regenerate_training_validation_xlsx.py</t>
         </is>
       </c>
     </row>
@@ -894,28 +894,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3220101515667749</v>
+        <v>0.32198058248425</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3220101515667775</v>
+        <v>0.3219805824842527</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2854435506979248</v>
+        <v>0.2854250095578111</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2854434050412846</v>
+        <v>0.2854248639011709</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3223218597365097</v>
+        <v>0.3222922906539849</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3223218597365123</v>
+        <v>0.3222922906539875</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3220101515667749</v>
+        <v>0.32198058248425</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3220101515667775</v>
+        <v>0.3219805824842527</v>
       </c>
     </row>
   </sheetData>
@@ -2045,22 +2045,22 @@
         <v>0.1979215802962014</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.01347735060089541</v>
+        <v>0.01348027709682978</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.01347735060089504</v>
+        <v>0.01348027709682941</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.01252112637738379</v>
+        <v>0.01252352415351241</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0125211263773839</v>
+        <v>0.01252352415351251</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01362238021099917</v>
+        <v>0.01362530670693354</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0136223802109988</v>
+        <v>0.01362530670693317</v>
       </c>
     </row>
     <row r="10">
@@ -2281,22 +2281,22 @@
         <v>0.2214368855780278</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.03285485831582285</v>
+        <v>0.03282236273736364</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.03285485831582838</v>
+        <v>0.03282236273736915</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.02423010487578198</v>
+        <v>0.02420916595953973</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.02423010487578634</v>
+        <v>0.02420916595954407</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.03307053796629154</v>
+        <v>0.03303804238783233</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03307053796629708</v>
+        <v>0.03303804238783784</v>
       </c>
     </row>
     <row r="12">
@@ -2987,22 +2987,22 @@
         <v>1.849974143672589</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.3220101515667749</v>
+        <v>0.32198058248425</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.3220101515667775</v>
+        <v>0.3219805824842527</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.2854435506979248</v>
+        <v>0.2854250095578111</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.2854434050412846</v>
+        <v>0.2854248639011709</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.3223218597365097</v>
+        <v>0.3222922906539849</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.3223218597365123</v>
+        <v>0.3222922906539875</v>
       </c>
     </row>
   </sheetData>
@@ -3758,13 +3758,13 @@
         <v>0.3175449753524632</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05060709057092678</v>
+        <v>0.05061001706686115</v>
       </c>
       <c r="R6" t="n">
-        <v>0.04809405311382543</v>
+        <v>0.04809645088995405</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05088755805389816</v>
+        <v>0.05089048454983253</v>
       </c>
     </row>
     <row r="7">
@@ -3819,13 +3819,13 @@
         <v>0.3344486867673974</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.05639695484051561</v>
+        <v>0.0563644592620564</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0476869701336643</v>
+        <v>0.04766603121742205</v>
       </c>
       <c r="S7" t="n">
-        <v>0.05681530810888252</v>
+        <v>0.05678281253042331</v>
       </c>
     </row>
     <row r="8">

--- a/example/training/training_validation_reference.xlsx
+++ b/example/training/training_validation_reference.xlsx
@@ -490,7 +490,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Worst relative gap plugin vs reference: 2.4e-13 on the ANP movements, 4.4e-05 on movement 11 (CUSTOM profile, supplied track).</t>
+          <t>Worst relative gap plugin vs reference: 2.4e-13 on the ANP movements, 4.1e-06 on movement 11 (CUSTOM profile, supplied track).</t>
         </is>
       </c>
     </row>
@@ -745,10 +745,10 @@
         <v>22.41416778264804</v>
       </c>
       <c r="D3" t="n">
-        <v>23.65126116177226</v>
+        <v>23.33770314995289</v>
       </c>
       <c r="E3" t="n">
-        <v>23.65119517992509</v>
+        <v>23.33770300719163</v>
       </c>
       <c r="F3" t="n">
         <v>21.94877074704628</v>
@@ -776,10 +776,10 @@
         <v>7702.95181693998</v>
       </c>
       <c r="D4" t="n">
-        <v>6009.303801314025</v>
+        <v>6385.836677226731</v>
       </c>
       <c r="E4" t="n">
-        <v>6009.294901128162</v>
+        <v>6385.835011126059</v>
       </c>
       <c r="F4" t="n">
         <v>7708.835474860139</v>
@@ -807,10 +807,10 @@
         <v>1.227822241879149</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2542543505182</v>
+        <v>1.252468181913424</v>
       </c>
       <c r="E5" t="n">
-        <v>1.254253465879471</v>
+        <v>1.252468170492528</v>
       </c>
       <c r="F5" t="n">
         <v>1.237476793718553</v>
@@ -838,10 +838,10 @@
         <v>31.84088970009263</v>
       </c>
       <c r="D6" t="n">
-        <v>17.4610078635899</v>
+        <v>18.72134446485447</v>
       </c>
       <c r="E6" t="n">
-        <v>17.46099724968429</v>
+        <v>18.7213383372177</v>
       </c>
       <c r="F6" t="n">
         <v>30.05600124882837</v>
@@ -869,10 +869,10 @@
         <v>1.848562177486793</v>
       </c>
       <c r="D7" t="n">
-        <v>1.442118811610278</v>
+        <v>1.532479552470924</v>
       </c>
       <c r="E7" t="n">
-        <v>1.442116675734661</v>
+        <v>1.532479152638397</v>
       </c>
       <c r="F7" t="n">
         <v>1.849974143672607</v>
@@ -900,10 +900,10 @@
         <v>0.3219805824842527</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2854250095578111</v>
+        <v>0.2916112707090255</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2854248639011709</v>
+        <v>0.291611243442336</v>
       </c>
       <c r="F8" t="n">
         <v>0.3222922906539849</v>
@@ -2551,10 +2551,10 @@
         <v>1.239981802111557</v>
       </c>
       <c r="E14" t="n">
-        <v>1.517123059722133</v>
+        <v>1.203565047902762</v>
       </c>
       <c r="F14" t="n">
-        <v>1.517057077875044</v>
+        <v>1.203564905141588</v>
       </c>
       <c r="G14" t="n">
         <v>1.229304479945856</v>
@@ -2569,10 +2569,10 @@
         <v>896.6548282456466</v>
       </c>
       <c r="K14" t="n">
-        <v>204.6423022099099</v>
+        <v>581.1751781226151</v>
       </c>
       <c r="L14" t="n">
-        <v>204.6334020241235</v>
+        <v>581.1735120220202</v>
       </c>
       <c r="M14" t="n">
         <v>881.5683619073927</v>
@@ -2587,10 +2587,10 @@
         <v>0.02041703055851676</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02034053108272857</v>
+        <v>0.01855436247795308</v>
       </c>
       <c r="R14" t="n">
-        <v>0.02033964644400199</v>
+        <v>0.01855435105705928</v>
       </c>
       <c r="S14" t="n">
         <v>0.02061351704140056</v>
@@ -2605,10 +2605,10 @@
         <v>3.836516818567063</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2440459320356641</v>
+        <v>1.50438253330024</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2440353181297802</v>
+        <v>1.504376405663195</v>
       </c>
       <c r="Y14" t="n">
         <v>4.109231807499004</v>
@@ -2623,10 +2623,10 @@
         <v>0.2151801336872796</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.04911026691704524</v>
+        <v>0.1394710077776911</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.04910813104144738</v>
+        <v>0.1394706079451831</v>
       </c>
       <c r="AE14" t="n">
         <v>0.2115596682179912</v>
@@ -2641,10 +2641,10 @@
         <v>0.01469376702111024</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.003337385138824306</v>
+        <v>0.009523646290038726</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.003337239482182449</v>
+        <v>0.009523619023347505</v>
       </c>
       <c r="AK14" t="n">
         <v>0.01444821479277915</v>
@@ -2903,10 +2903,10 @@
         <v>22.41416778264804</v>
       </c>
       <c r="E17" t="n">
-        <v>23.65126116177226</v>
+        <v>23.33770314995289</v>
       </c>
       <c r="F17" t="n">
-        <v>23.65119517992509</v>
+        <v>23.33770300719163</v>
       </c>
       <c r="G17" t="n">
         <v>21.94877074704628</v>
@@ -2921,10 +2921,10 @@
         <v>7702.95181693998</v>
       </c>
       <c r="K17" t="n">
-        <v>6009.303801314025</v>
+        <v>6385.836677226731</v>
       </c>
       <c r="L17" t="n">
-        <v>6009.294901128162</v>
+        <v>6385.835011126059</v>
       </c>
       <c r="M17" t="n">
         <v>7708.835474860139</v>
@@ -2939,10 +2939,10 @@
         <v>1.227822241879149</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.2542543505182</v>
+        <v>1.252468181913424</v>
       </c>
       <c r="R17" t="n">
-        <v>1.254253465879471</v>
+        <v>1.252468170492528</v>
       </c>
       <c r="S17" t="n">
         <v>1.237476793718553</v>
@@ -2957,10 +2957,10 @@
         <v>31.84088970009263</v>
       </c>
       <c r="W17" t="n">
-        <v>17.4610078635899</v>
+        <v>18.72134446485447</v>
       </c>
       <c r="X17" t="n">
-        <v>17.46099724968429</v>
+        <v>18.7213383372177</v>
       </c>
       <c r="Y17" t="n">
         <v>30.05600124882837</v>
@@ -2975,10 +2975,10 @@
         <v>1.848562177486793</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.442118811610278</v>
+        <v>1.532479552470924</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.442116675734661</v>
+        <v>1.532479152638397</v>
       </c>
       <c r="AE17" t="n">
         <v>1.849974143672607</v>
@@ -2993,10 +2993,10 @@
         <v>0.3219805824842527</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.2854250095578111</v>
+        <v>0.2916112707090255</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.2854248639011709</v>
+        <v>0.291611243442336</v>
       </c>
       <c r="AK17" t="n">
         <v>0.3222922906539849</v>
@@ -3899,7 +3899,7 @@
         <v>3.650223216030941</v>
       </c>
       <c r="C9" t="n">
-        <v>3.956774968272925</v>
+        <v>3.643216956453553</v>
       </c>
       <c r="D9" t="n">
         <v>3.351670141385034</v>
@@ -3908,7 +3908,7 @@
         <v>1320.520166205253</v>
       </c>
       <c r="F9" t="n">
-        <v>571.2832888566306</v>
+        <v>947.8161647693357</v>
       </c>
       <c r="G9" t="n">
         <v>1291.724350092784</v>
@@ -3917,7 +3917,7 @@
         <v>0.2283253103540685</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2301924480515556</v>
+        <v>0.2284062794467801</v>
       </c>
       <c r="J9" t="n">
         <v>0.2241571387179871</v>
@@ -3926,7 +3926,7 @@
         <v>4.69067743936141</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8080439761362889</v>
+        <v>2.068380577400865</v>
       </c>
       <c r="M9" t="n">
         <v>4.824306176199871</v>
@@ -3935,7 +3935,7 @@
         <v>0.316899766721548</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1370971421745371</v>
+        <v>0.2274578830351829</v>
       </c>
       <c r="P9" t="n">
         <v>0.3099893176105575</v>
@@ -3944,7 +3944,7 @@
         <v>0.03752844288525238</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02503872770431084</v>
+        <v>0.03122498885552526</v>
       </c>
       <c r="S9" t="n">
         <v>0.03693974032739044</v>

--- a/example/training/training_validation_reference.xlsx
+++ b/example/training/training_validation_reference.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Made on 2026-10-20 by openalaqs_standalone/validation/tools/regenerate_training_validation_xlsx.py</t>
+          <t>Made on 2026-10-24 by openalaqs_standalone/validation/tools/regenerate_training_validation_xlsx.py</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Worst relative gap plugin vs reference: 2.4e-13 on the ANP movements, 4.1e-06 on movement 11 (CUSTOM profile, supplied track).</t>
+          <t>Worst relative gap plugin vs reference: 2.5e-13 on the ANP movements, 1.2e-15 on movement 11 (CUSTOM profile, supplied track).</t>
         </is>
       </c>
     </row>
@@ -745,16 +745,16 @@
         <v>22.41416778264804</v>
       </c>
       <c r="D3" t="n">
-        <v>23.33770314995289</v>
+        <v>22.94327126929209</v>
       </c>
       <c r="E3" t="n">
-        <v>23.33770300719163</v>
+        <v>22.94327126929201</v>
       </c>
       <c r="F3" t="n">
-        <v>21.94877074704628</v>
+        <v>21.31312804967991</v>
       </c>
       <c r="G3" t="n">
-        <v>21.94877074704612</v>
+        <v>21.31312804967976</v>
       </c>
       <c r="H3" t="n">
         <v>22.41416778264819</v>
@@ -776,16 +776,16 @@
         <v>7702.95181693998</v>
       </c>
       <c r="D4" t="n">
-        <v>6385.836677226731</v>
+        <v>6047.161220537516</v>
       </c>
       <c r="E4" t="n">
-        <v>6385.835011126059</v>
+        <v>6047.161220537442</v>
       </c>
       <c r="F4" t="n">
-        <v>7708.835474860139</v>
+        <v>7661.823341622828</v>
       </c>
       <c r="G4" t="n">
-        <v>7708.835474860065</v>
+        <v>7661.823341622754</v>
       </c>
       <c r="H4" t="n">
         <v>7702.951816940053</v>
@@ -807,16 +807,16 @@
         <v>1.227822241879149</v>
       </c>
       <c r="D5" t="n">
-        <v>1.252468181913424</v>
+        <v>1.203898409654131</v>
       </c>
       <c r="E5" t="n">
-        <v>1.252468170492528</v>
+        <v>1.203898409654129</v>
       </c>
       <c r="F5" t="n">
-        <v>1.237476793718553</v>
+        <v>1.176527737589143</v>
       </c>
       <c r="G5" t="n">
-        <v>1.23747679371855</v>
+        <v>1.17652773758914</v>
       </c>
       <c r="H5" t="n">
         <v>1.227822241879152</v>
@@ -838,16 +838,16 @@
         <v>31.84088970009263</v>
       </c>
       <c r="D6" t="n">
-        <v>18.72134446485447</v>
+        <v>16.61457596321196</v>
       </c>
       <c r="E6" t="n">
-        <v>18.7213383372177</v>
+        <v>16.614575963212</v>
       </c>
       <c r="F6" t="n">
-        <v>30.05600124882837</v>
+        <v>30.14120745540007</v>
       </c>
       <c r="G6" t="n">
-        <v>30.05600124882807</v>
+        <v>30.14120745539971</v>
       </c>
       <c r="H6" t="n">
         <v>30.69751460020806</v>
@@ -869,16 +869,16 @@
         <v>1.848562177486793</v>
       </c>
       <c r="D7" t="n">
-        <v>1.532479552470924</v>
+        <v>1.451203873412158</v>
       </c>
       <c r="E7" t="n">
-        <v>1.532479152638397</v>
+        <v>1.45120387341214</v>
       </c>
       <c r="F7" t="n">
-        <v>1.849974143672607</v>
+        <v>1.838692124331093</v>
       </c>
       <c r="G7" t="n">
-        <v>1.849974143672589</v>
+        <v>1.838692124331076</v>
       </c>
       <c r="H7" t="n">
         <v>1.84856217748681</v>
@@ -894,28 +894,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.32198058248425</v>
+        <v>0.3219438746866928</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3219805824842527</v>
+        <v>0.3219438746866953</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2916112707090255</v>
+        <v>0.2832440172940929</v>
       </c>
       <c r="E8" t="n">
-        <v>0.291611243442336</v>
+        <v>0.2832440172940944</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3222922906539849</v>
+        <v>0.3210750171147053</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3222922906539875</v>
+        <v>0.3210750171147078</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32198058248425</v>
+        <v>0.3219438746866928</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3219805824842527</v>
+        <v>0.3219438746866953</v>
       </c>
     </row>
   </sheetData>
@@ -1371,16 +1371,16 @@
         <v>1.378813062957872</v>
       </c>
       <c r="E4" t="n">
-        <v>1.632835873001475</v>
+        <v>1.570211083962909</v>
       </c>
       <c r="F4" t="n">
-        <v>1.632835873001435</v>
+        <v>1.570211083962863</v>
       </c>
       <c r="G4" t="n">
-        <v>1.430577879312127</v>
+        <v>1.303604415167373</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4305778793121</v>
+        <v>1.303604415167346</v>
       </c>
       <c r="I4" t="n">
         <v>490.1490905873051</v>
@@ -1389,16 +1389,16 @@
         <v>490.1490905872779</v>
       </c>
       <c r="K4" t="n">
-        <v>405.6001768750213</v>
+        <v>350.770236744953</v>
       </c>
       <c r="L4" t="n">
-        <v>405.6001768750009</v>
+        <v>350.7702367449347</v>
       </c>
       <c r="M4" t="n">
-        <v>500.9344436657162</v>
+        <v>482.2424050395727</v>
       </c>
       <c r="N4" t="n">
-        <v>500.9344436656888</v>
+        <v>482.2424050395454</v>
       </c>
       <c r="O4" t="n">
         <v>0.01895165692061811</v>
@@ -1407,16 +1407,16 @@
         <v>0.01895165692061777</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02240262415216688</v>
+        <v>0.02149078444377348</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02240262415216629</v>
+        <v>0.02149078444377282</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01966059014354284</v>
+        <v>0.01796124010512681</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01966059014354243</v>
+        <v>0.01796124010512641</v>
       </c>
       <c r="U4" t="n">
         <v>1.146122365269231</v>
@@ -1425,16 +1425,16 @@
         <v>1.146122365269156</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8058823641523013</v>
+        <v>0.6540121709216299</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8058823641522543</v>
+        <v>0.6540121709215905</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.184691312222633</v>
+        <v>1.15575152847595</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.184691312222558</v>
+        <v>1.155751528475874</v>
       </c>
       <c r="AA4" t="n">
         <v>0.1176264751126509</v>
@@ -1443,16 +1443,16 @@
         <v>0.1176264751126444</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.09733634118082393</v>
+        <v>0.08417819662442014</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.09733634118081905</v>
+        <v>0.08417819662441574</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1202147550662845</v>
+        <v>0.1157290207081359</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.120214755066278</v>
+        <v>0.1157290207081294</v>
       </c>
       <c r="AG4" t="n">
         <v>0.03712973997003137</v>
@@ -1461,16 +1461,16 @@
         <v>0.0371297399700309</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0356701716489414</v>
+        <v>0.03474611907500818</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.03567017164894105</v>
+        <v>0.03474611907500786</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.03730528588133773</v>
+        <v>0.03700104818685111</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03730528588133726</v>
+        <v>0.03700104818685063</v>
       </c>
     </row>
     <row r="5">
@@ -1489,16 +1489,16 @@
         <v>1.215414648670439</v>
       </c>
       <c r="E5" t="n">
-        <v>1.228964391559609</v>
+        <v>1.094518729843991</v>
       </c>
       <c r="F5" t="n">
-        <v>1.228964391559607</v>
+        <v>1.09451872984399</v>
       </c>
       <c r="G5" t="n">
-        <v>1.231490660925493</v>
+        <v>1.100875537832213</v>
       </c>
       <c r="H5" t="n">
-        <v>1.231490660925491</v>
+        <v>1.100875537832211</v>
       </c>
       <c r="I5" t="n">
         <v>619.2711847860185</v>
@@ -1507,16 +1507,16 @@
         <v>619.2711847860041</v>
       </c>
       <c r="K5" t="n">
-        <v>597.2313179545268</v>
+        <v>527.2256563695905</v>
       </c>
       <c r="L5" t="n">
-        <v>597.2313179545213</v>
+        <v>527.2256563695844</v>
       </c>
       <c r="M5" t="n">
-        <v>630.8203587258831</v>
+        <v>610.8045461869204</v>
       </c>
       <c r="N5" t="n">
-        <v>630.8203587258687</v>
+        <v>610.804546186906</v>
       </c>
       <c r="O5" t="n">
         <v>0.01866143787839252</v>
@@ -1525,16 +1525,16 @@
         <v>0.01866143787839243</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01854634710651515</v>
+        <v>0.01650724818391679</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0185463471065151</v>
+        <v>0.01650724818391674</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01874844865578592</v>
+        <v>0.01701579282297456</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01874844865578582</v>
+        <v>0.01701579282297446</v>
       </c>
       <c r="U5" t="n">
         <v>4.181440045729932</v>
@@ -1543,16 +1543,16 @@
         <v>4.181440045729329</v>
       </c>
       <c r="W5" t="n">
-        <v>2.69013302961917</v>
+        <v>1.870353400893016</v>
       </c>
       <c r="X5" t="n">
-        <v>2.690133029619029</v>
+        <v>1.870353400892966</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.479763630921958</v>
+        <v>3.476152672202123</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.479763630921562</v>
+        <v>3.47615267220169</v>
       </c>
       <c r="AA5" t="n">
         <v>0.1486133260350092</v>
@@ -1561,16 +1561,16 @@
         <v>0.1486133260350058</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1433241764739354</v>
+        <v>0.1265241469149732</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.1433241764739341</v>
+        <v>0.1265241469149717</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.151384908492464</v>
+        <v>0.1465814935301865</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1513849084924606</v>
+        <v>0.146581493530183</v>
       </c>
       <c r="AG5" t="n">
         <v>0.01025643025501735</v>
@@ -1579,16 +1579,16 @@
         <v>0.01025643025501708</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.009884808647925734</v>
+        <v>0.008726604098357366</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.009884808647925611</v>
+        <v>0.008726604098357236</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.01044440836286135</v>
+        <v>0.01011862449402142</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01044440836286108</v>
+        <v>0.01011862449402114</v>
       </c>
     </row>
     <row r="6">
@@ -1607,16 +1607,16 @@
         <v>2.45980104308333</v>
       </c>
       <c r="E6" t="n">
-        <v>2.575307142304504</v>
+        <v>2.475837349181398</v>
       </c>
       <c r="F6" t="n">
-        <v>2.575307142304502</v>
+        <v>2.475837349181401</v>
       </c>
       <c r="G6" t="n">
-        <v>2.546332895381979</v>
+        <v>2.309501994795961</v>
       </c>
       <c r="H6" t="n">
-        <v>2.546332895381917</v>
+        <v>2.309501994795899</v>
       </c>
       <c r="I6" t="n">
         <v>462.8226583969787</v>
@@ -1625,16 +1625,16 @@
         <v>462.8226583969372</v>
       </c>
       <c r="K6" t="n">
-        <v>461.6558377888711</v>
+        <v>399.6852599573752</v>
       </c>
       <c r="L6" t="n">
-        <v>461.6558377888089</v>
+        <v>399.6852599573194</v>
       </c>
       <c r="M6" t="n">
-        <v>473.3176054306242</v>
+        <v>455.1288679914289</v>
       </c>
       <c r="N6" t="n">
-        <v>473.3176054305829</v>
+        <v>455.1288679913876</v>
       </c>
       <c r="O6" t="n">
         <v>0.2091411063916711</v>
@@ -1643,16 +1643,16 @@
         <v>0.2091411063916697</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2178583379569806</v>
+        <v>0.2048972723985031</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2178583379569796</v>
+        <v>0.2048972723985023</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2146792877065687</v>
+        <v>0.1921103358476111</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2146792877065669</v>
+        <v>0.1921103358476093</v>
       </c>
       <c r="U6" t="n">
         <v>0.952047052526225</v>
@@ -1661,16 +1661,16 @@
         <v>0.952047052526121</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9298334427391808</v>
+        <v>0.7293388792473904</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9298334427389773</v>
+        <v>0.7293388792472201</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9760940509823317</v>
+        <v>0.9550324725866584</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.976094050982228</v>
+        <v>0.955032472586555</v>
       </c>
       <c r="AA6" t="n">
         <v>0.11106865024328</v>
@@ -1679,16 +1679,16 @@
         <v>0.1110686502432701</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1107886354521558</v>
+        <v>0.09591687342913795</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.1107886354521409</v>
+        <v>0.09591687342912453</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1135872382602087</v>
+        <v>0.109222286630576</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1135872382601988</v>
+        <v>0.1092222866305661</v>
       </c>
       <c r="AG6" t="n">
         <v>0.02354209652469276</v>
@@ -1697,16 +1697,16 @@
         <v>0.02354209652469201</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.02359302466415088</v>
+        <v>0.02234272506869606</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.02359302466414975</v>
+        <v>0.02234272506869505</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.02380478910984933</v>
+        <v>0.0233495179738142</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.02380478910984857</v>
+        <v>0.02334951797381345</v>
       </c>
     </row>
     <row r="7">
@@ -1725,16 +1725,16 @@
         <v>2.345789062664485</v>
       </c>
       <c r="E7" t="n">
-        <v>2.326634843410293</v>
+        <v>2.071947412424934</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3266348434103</v>
+        <v>2.07194741242494</v>
       </c>
       <c r="G7" t="n">
-        <v>2.364219089796864</v>
+        <v>2.12107909846831</v>
       </c>
       <c r="H7" t="n">
-        <v>2.364219089796869</v>
+        <v>2.121079098468316</v>
       </c>
       <c r="I7" t="n">
         <v>684.9000076076563</v>
@@ -1743,16 +1743,16 @@
         <v>684.9000076076826</v>
       </c>
       <c r="K7" t="n">
-        <v>545.5513858679956</v>
+        <v>481.8056777341648</v>
       </c>
       <c r="L7" t="n">
-        <v>545.5513858680213</v>
+        <v>481.8056777341915</v>
       </c>
       <c r="M7" t="n">
-        <v>696.0684395495034</v>
+        <v>676.7124889623747</v>
       </c>
       <c r="N7" t="n">
-        <v>696.0684395495296</v>
+        <v>676.7124889624008</v>
       </c>
       <c r="O7" t="n">
         <v>0.2216070221405289</v>
@@ -1761,16 +1761,16 @@
         <v>0.221607022140529</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2230321082553342</v>
+        <v>0.19862292903492</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2230321082553347</v>
+        <v>0.1986229290349205</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2262018639746835</v>
+        <v>0.2027665652072529</v>
       </c>
       <c r="T7" t="n">
-        <v>0.226201863974684</v>
+        <v>0.2027665652072534</v>
       </c>
       <c r="U7" t="n">
         <v>3.321360497066342</v>
@@ -1779,16 +1779,16 @@
         <v>3.321360497066525</v>
       </c>
       <c r="W7" t="n">
-        <v>1.933417175668677</v>
+        <v>1.584143183482866</v>
       </c>
       <c r="X7" t="n">
-        <v>1.933417175668826</v>
+        <v>1.584143183483013</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.338619877407057</v>
+        <v>3.316159485664065</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.338619877407233</v>
+        <v>3.316159485664237</v>
       </c>
       <c r="AA7" t="n">
         <v>0.1643629973953133</v>
@@ -1797,16 +1797,16 @@
         <v>0.1643629973953196</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1309219740377012</v>
+        <v>0.1156242144471287</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1309219740377074</v>
+        <v>0.115624214447135</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1670432090025223</v>
+        <v>0.1623981483796605</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1670432090025285</v>
+        <v>0.1623981483796668</v>
       </c>
       <c r="AG7" t="n">
         <v>0.02467646364099519</v>
@@ -1815,16 +1815,16 @@
         <v>0.02467646364099637</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0190097502344173</v>
+        <v>0.01678344606828333</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01900975023441841</v>
+        <v>0.01678344606828446</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.02495601381400163</v>
+        <v>0.02447152688123343</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02495601381400281</v>
+        <v>0.02447152688123461</v>
       </c>
     </row>
     <row r="8">
@@ -1843,16 +1843,16 @@
         <v>1.378813062957872</v>
       </c>
       <c r="E8" t="n">
-        <v>1.625026308993482</v>
+        <v>1.585541810993691</v>
       </c>
       <c r="F8" t="n">
-        <v>1.625026308993442</v>
+        <v>1.585541810993647</v>
       </c>
       <c r="G8" t="n">
-        <v>1.417960210674832</v>
+        <v>1.330294811361096</v>
       </c>
       <c r="H8" t="n">
-        <v>1.417960210674805</v>
+        <v>1.330294811361069</v>
       </c>
       <c r="I8" t="n">
         <v>490.1490905873051</v>
@@ -1861,16 +1861,16 @@
         <v>490.1490905872779</v>
       </c>
       <c r="K8" t="n">
-        <v>399.8046537772931</v>
+        <v>359.2993559399889</v>
       </c>
       <c r="L8" t="n">
-        <v>399.8046537772732</v>
+        <v>359.2993559399702</v>
       </c>
       <c r="M8" t="n">
-        <v>498.4702486717957</v>
+        <v>485.919679743594</v>
       </c>
       <c r="N8" t="n">
-        <v>498.4702486717683</v>
+        <v>485.9196797435667</v>
       </c>
       <c r="O8" t="n">
         <v>0.01895165692061811</v>
@@ -1879,16 +1879,16 @@
         <v>0.01895165692061777</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02229550012676938</v>
+        <v>0.02171719002895577</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02229550012676879</v>
+        <v>0.02171719002895514</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0194887907696156</v>
+        <v>0.01831625177736925</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0194887907696152</v>
+        <v>0.01831625177736886</v>
       </c>
       <c r="U8" t="n">
         <v>1.146122365269231</v>
@@ -1897,16 +1897,16 @@
         <v>1.146122365269156</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8004759918700028</v>
+        <v>0.6846597820987019</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8004759918699562</v>
+        <v>0.6846597820986602</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.199336953562032</v>
+        <v>1.179759826175719</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.199336953561955</v>
+        <v>1.179759826175642</v>
       </c>
       <c r="AA8" t="n">
         <v>0.1176264751126509</v>
@@ -1915,16 +1915,16 @@
         <v>0.1176264751126444</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.09594552567894701</v>
+        <v>0.08622502328592759</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.09594552567894217</v>
+        <v>0.08622502328592312</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.1196233950562562</v>
+        <v>0.1166114968154294</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1196233950562496</v>
+        <v>0.1166114968154229</v>
       </c>
       <c r="AG8" t="n">
         <v>0.03712973997003137</v>
@@ -1933,16 +1933,16 @@
         <v>0.0371297399700309</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.03557292673644164</v>
+        <v>0.0348891874213325</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0355729267364413</v>
+        <v>0.03488918742133218</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.03726517784289898</v>
+        <v>0.03706090070483063</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.03726517784289852</v>
+        <v>0.03706090070483017</v>
       </c>
     </row>
     <row r="9">
@@ -1961,16 +1961,16 @@
         <v>1.231587047769073</v>
       </c>
       <c r="E9" t="n">
-        <v>1.235926748147279</v>
+        <v>1.142801714106447</v>
       </c>
       <c r="F9" t="n">
-        <v>1.235926748147278</v>
+        <v>1.142801714106446</v>
       </c>
       <c r="G9" t="n">
-        <v>1.240978847151445</v>
+        <v>1.153014676130353</v>
       </c>
       <c r="H9" t="n">
-        <v>1.240978847151442</v>
+        <v>1.153014676130349</v>
       </c>
       <c r="I9" t="n">
         <v>815.8280353694297</v>
@@ -1979,16 +1979,16 @@
         <v>815.8280353694066</v>
       </c>
       <c r="K9" t="n">
-        <v>758.20907819808</v>
+        <v>680.4372625991382</v>
       </c>
       <c r="L9" t="n">
-        <v>758.2090781980856</v>
+        <v>680.4372625991498</v>
       </c>
       <c r="M9" t="n">
-        <v>824.7384995332095</v>
+        <v>811.299096804132</v>
       </c>
       <c r="N9" t="n">
-        <v>824.7384995331862</v>
+        <v>811.2990968041087</v>
       </c>
       <c r="O9" t="n">
         <v>0.01990546857828753</v>
@@ -1997,16 +1997,16 @@
         <v>0.01990546857828738</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01948707956990367</v>
+        <v>0.01796155970766675</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01948707956990369</v>
+        <v>0.01796155970766678</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01989124749023696</v>
+        <v>0.01877859666957921</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01989124749023679</v>
+        <v>0.01877859666957903</v>
       </c>
       <c r="U9" t="n">
         <v>5.013696583960182</v>
@@ -2015,16 +2015,16 @@
         <v>5.013696583960192</v>
       </c>
       <c r="W9" t="n">
-        <v>3.384686427096209</v>
+        <v>2.615953042014762</v>
       </c>
       <c r="X9" t="n">
-        <v>3.384686427096627</v>
+        <v>2.615953042014984</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.568400564985925</v>
+        <v>4.578770938457324</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.56840056498585</v>
+        <v>4.578770938457199</v>
       </c>
       <c r="AA9" t="n">
         <v>0.1957832380829283</v>
@@ -2033,34 +2033,34 @@
         <v>0.1957832380829227</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1819557823926367</v>
+        <v>0.1632920233289337</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.181955782392638</v>
+        <v>0.1632920233289364</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.197921580296207</v>
+        <v>0.1946963788197612</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1979215802962014</v>
+        <v>0.1946963788197556</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.01348027709682978</v>
+        <v>0.01347958160509898</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.01348027709682941</v>
+        <v>0.01347958160509861</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.01252352415351241</v>
+        <v>0.01124058202563656</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01252352415351251</v>
+        <v>0.01124058202563676</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01362530670693354</v>
+        <v>0.0134058671293729</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01362530670693317</v>
+        <v>0.01340586712937253</v>
       </c>
     </row>
     <row r="10">
@@ -2079,16 +2079,16 @@
         <v>2.45980104308333</v>
       </c>
       <c r="E10" t="n">
-        <v>2.562966326706932</v>
+        <v>2.502559066085736</v>
       </c>
       <c r="F10" t="n">
-        <v>2.56296632670693</v>
+        <v>2.502559066085738</v>
       </c>
       <c r="G10" t="n">
-        <v>2.524463998938689</v>
+        <v>2.361399994346058</v>
       </c>
       <c r="H10" t="n">
-        <v>2.524463998938629</v>
+        <v>2.361399994345998</v>
       </c>
       <c r="I10" t="n">
         <v>462.8226583969787</v>
@@ -2097,16 +2097,16 @@
         <v>462.8226583969372</v>
       </c>
       <c r="K10" t="n">
-        <v>455.0649757409302</v>
+        <v>409.4045802120594</v>
       </c>
       <c r="L10" t="n">
-        <v>455.0649757408688</v>
+        <v>409.4045802120022</v>
       </c>
       <c r="M10" t="n">
-        <v>470.9197612660657</v>
+        <v>458.7071285236798</v>
       </c>
       <c r="N10" t="n">
-        <v>470.9197612660244</v>
+        <v>458.7071285236385</v>
       </c>
       <c r="O10" t="n">
         <v>0.2091411063916711</v>
@@ -2115,16 +2115,16 @@
         <v>0.2091411063916697</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2168119085164784</v>
+        <v>0.2083022280293174</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2168119085164773</v>
+        <v>0.2083022280293166</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2131293132794072</v>
+        <v>0.1976670089451801</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2131293132794056</v>
+        <v>0.1976670089451785</v>
       </c>
       <c r="U10" t="n">
         <v>0.952047052526225</v>
@@ -2133,16 +2133,16 @@
         <v>0.952047052526121</v>
       </c>
       <c r="W10" t="n">
-        <v>0.9236108281642439</v>
+        <v>0.7704076192415948</v>
       </c>
       <c r="X10" t="n">
-        <v>0.9236108281640419</v>
+        <v>0.7704076192414147</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.9898663981330998</v>
+        <v>0.9761116316075922</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.989866398132994</v>
+        <v>0.9761116316074864</v>
       </c>
       <c r="AA10" t="n">
         <v>0.11106865024328</v>
@@ -2151,16 +2151,16 @@
         <v>0.1110686502432701</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1092069537036003</v>
+        <v>0.09824932574620666</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1092069537035856</v>
+        <v>0.09824932574619295</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1130118011894014</v>
+        <v>0.1100810012166605</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1130118011893914</v>
+        <v>0.1100810012166506</v>
       </c>
       <c r="AG10" t="n">
         <v>0.02354209652469276</v>
@@ -2169,16 +2169,16 @@
         <v>0.02354209652469201</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.02345686525788232</v>
+        <v>0.02254380497906484</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.02345686525788121</v>
+        <v>0.0225438049790638</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.02374477014259098</v>
+        <v>0.02343908321950504</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02374477014259023</v>
+        <v>0.02343908321950428</v>
       </c>
     </row>
     <row r="11">
@@ -2197,16 +2197,16 @@
         <v>2.401640859208391</v>
       </c>
       <c r="E11" t="n">
-        <v>2.354305633061668</v>
+        <v>2.175956407955791</v>
       </c>
       <c r="F11" t="n">
-        <v>2.354305633061694</v>
+        <v>2.175956407955815</v>
       </c>
       <c r="G11" t="n">
-        <v>2.412504918802183</v>
+        <v>2.250406913145358</v>
       </c>
       <c r="H11" t="n">
-        <v>2.412504918802216</v>
+        <v>2.250406913145392</v>
       </c>
       <c r="I11" t="n">
         <v>914.1099778396826</v>
@@ -2215,16 +2215,16 @@
         <v>914.1099778398153</v>
       </c>
       <c r="K11" t="n">
-        <v>691.8811631423655</v>
+        <v>621.1925280137139</v>
       </c>
       <c r="L11" t="n">
-        <v>691.8811631424701</v>
+        <v>621.192528013808</v>
       </c>
       <c r="M11" t="n">
-        <v>922.7266904376233</v>
+        <v>909.7303449413726</v>
       </c>
       <c r="N11" t="n">
-        <v>922.726690437756</v>
+        <v>909.7303449415052</v>
       </c>
       <c r="O11" t="n">
         <v>0.2281351542041002</v>
@@ -2233,16 +2233,16 @@
         <v>0.2281351542041025</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2252368181434342</v>
+        <v>0.208204178361832</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2252368181434364</v>
+        <v>0.208204178361834</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2301451916396223</v>
+        <v>0.2144831366308317</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2301451916396251</v>
+        <v>0.2144831366308345</v>
       </c>
       <c r="U11" t="n">
         <v>4.497874964523046</v>
@@ -2251,16 +2251,16 @@
         <v>4.497874964523856</v>
       </c>
       <c r="W11" t="n">
-        <v>2.557134136480725</v>
+        <v>2.137463708699487</v>
       </c>
       <c r="X11" t="n">
-        <v>2.557134136481259</v>
+        <v>2.13746370869994</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.632064210096298</v>
+        <v>4.617006957566914</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.632064210097116</v>
+        <v>4.617006957567733</v>
       </c>
       <c r="AA11" t="n">
         <v>0.2193690381629573</v>
@@ -2269,34 +2269,34 @@
         <v>0.2193690381629891</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1660383421700574</v>
+        <v>0.1490744119284556</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.1660383421700826</v>
+        <v>0.1490744119284782</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.221436885577996</v>
+        <v>0.2183180094249495</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.2214368855780278</v>
+        <v>0.2183180094249814</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.03282236273736364</v>
+        <v>0.03278635043153719</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.03282236273736915</v>
+        <v>0.03278635043154266</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.02420916595953973</v>
+        <v>0.02170188359338025</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.02420916595954407</v>
+        <v>0.02170188359338414</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.03303804238783233</v>
+        <v>0.03267672652544167</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03303804238783784</v>
+        <v>0.03267672652544714</v>
       </c>
     </row>
     <row r="12">
@@ -2315,16 +2315,16 @@
         <v>1.341212842926714</v>
       </c>
       <c r="E12" t="n">
-        <v>1.479706289942876</v>
+        <v>1.560203255311646</v>
       </c>
       <c r="F12" t="n">
-        <v>1.479706289942836</v>
+        <v>1.560203255311614</v>
       </c>
       <c r="G12" t="n">
-        <v>1.114410376065972</v>
+        <v>1.215024073256311</v>
       </c>
       <c r="H12" t="n">
-        <v>1.114410376065968</v>
+        <v>1.21502407325631</v>
       </c>
       <c r="I12" t="n">
         <v>445.3126017954343</v>
@@ -2333,16 +2333,16 @@
         <v>445.3126017954071</v>
       </c>
       <c r="K12" t="n">
-        <v>331.9457703044816</v>
+        <v>357.9439694212697</v>
       </c>
       <c r="L12" t="n">
-        <v>331.9457703044641</v>
+        <v>357.9439694212503</v>
       </c>
       <c r="M12" t="n">
-        <v>431.2239001263054</v>
+        <v>446.9509474291033</v>
       </c>
       <c r="N12" t="n">
-        <v>431.2239001262781</v>
+        <v>446.9509474290759</v>
       </c>
       <c r="O12" t="n">
         <v>0.01838410642958177</v>
@@ -2351,16 +2351,16 @@
         <v>0.01838410642958143</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02033671589172297</v>
+        <v>0.02146408851774437</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0203367158917224</v>
+        <v>0.0214640885177439</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01656282724585744</v>
+        <v>0.01795907766165484</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01656282724585724</v>
+        <v>0.01795907766165467</v>
       </c>
       <c r="U12" t="n">
         <v>1.021970695355032</v>
@@ -2369,16 +2369,16 @@
         <v>1.021970695354957</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5124814119682357</v>
+        <v>0.5642557543065081</v>
       </c>
       <c r="X12" t="n">
-        <v>0.5124814119682047</v>
+        <v>0.564255754306471</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.8395402819178565</v>
+        <v>0.8561582497235692</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.839540281917793</v>
+        <v>0.8561582497235054</v>
       </c>
       <c r="AA12" t="n">
         <v>0.1068665691283385</v>
@@ -2387,16 +2387,16 @@
         <v>0.106866569128332</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.07966068210528497</v>
+        <v>0.08589975625662208</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.07966068210528079</v>
+        <v>0.0858997562566174</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.1034855482347413</v>
+        <v>0.1072597409725906</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1034855482347347</v>
+        <v>0.107259740972584</v>
       </c>
       <c r="AG12" t="n">
         <v>0.03636073231494315</v>
@@ -2405,16 +2405,16 @@
         <v>0.03636073231494269</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.03442866310285013</v>
+        <v>0.03486080606244163</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.03442866310284985</v>
+        <v>0.0348608060624413</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.03613142002858126</v>
+        <v>0.03638739856084223</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0361314200285808</v>
+        <v>0.03638739856084176</v>
       </c>
     </row>
     <row r="13">
@@ -2433,16 +2433,16 @@
         <v>1.209859455959314</v>
       </c>
       <c r="E13" t="n">
-        <v>1.193107555203807</v>
+        <v>1.303000219127626</v>
       </c>
       <c r="F13" t="n">
-        <v>1.193107555203805</v>
+        <v>1.303000219127626</v>
       </c>
       <c r="G13" t="n">
-        <v>1.199751393987417</v>
+        <v>1.307060066139829</v>
       </c>
       <c r="H13" t="n">
-        <v>1.199751393987414</v>
+        <v>1.307060066139828</v>
       </c>
       <c r="I13" t="n">
         <v>551.7542272200436</v>
@@ -2451,16 +2451,16 @@
         <v>551.7542272200184</v>
       </c>
       <c r="K13" t="n">
-        <v>459.130545553183</v>
+        <v>506.4698261996193</v>
       </c>
       <c r="L13" t="n">
-        <v>459.1305455531694</v>
+        <v>506.4698261996035</v>
       </c>
       <c r="M13" t="n">
-        <v>536.6677608817897</v>
+        <v>553.5086008190625</v>
       </c>
       <c r="N13" t="n">
-        <v>536.6677608817644</v>
+        <v>553.508600819037</v>
       </c>
       <c r="O13" t="n">
         <v>0.01823411536215217</v>
@@ -2469,16 +2469,16 @@
         <v>0.01823411536215202</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01771776306203666</v>
+        <v>0.01938517497797719</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01771776306203655</v>
+        <v>0.01938517497797711</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01824927016472546</v>
+        <v>0.0197099627389534</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01824927016472527</v>
+        <v>0.01970996273895325</v>
       </c>
       <c r="U13" t="n">
         <v>3.89556128236514</v>
@@ -2487,16 +2487,16 @@
         <v>3.89556128236449</v>
       </c>
       <c r="W13" t="n">
-        <v>1.60282786217157</v>
+        <v>2.281954518772726</v>
       </c>
       <c r="X13" t="n">
-        <v>1.602827862171448</v>
+        <v>2.281954518772515</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.18377864137998</v>
+        <v>3.203229913702943</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.183778641379583</v>
+        <v>3.203229913702576</v>
       </c>
       <c r="AA13" t="n">
         <v>0.132410538186724</v>
@@ -2505,16 +2505,16 @@
         <v>0.132410538186718</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1101826132641775</v>
+        <v>0.1215431417722213</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1101826132641742</v>
+        <v>0.1215431417722175</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1287900727174356</v>
+        <v>0.1328315545395974</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1287900727174295</v>
+        <v>0.1328315545395913</v>
       </c>
       <c r="AG13" t="n">
         <v>0.009151476544678629</v>
@@ -2523,16 +2523,16 @@
         <v>0.009151476544678178</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.007608721141518298</v>
+        <v>0.00839311117126498</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.007608721141518044</v>
+        <v>0.00839311117126469</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.008905924316347532</v>
+        <v>0.009180031299443963</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.00890592431634708</v>
+        <v>0.009180031299443512</v>
       </c>
     </row>
     <row r="14">
@@ -2551,16 +2551,16 @@
         <v>1.239981802111557</v>
       </c>
       <c r="E14" t="n">
-        <v>1.203565047902762</v>
+        <v>1.311085156926007</v>
       </c>
       <c r="F14" t="n">
-        <v>1.203564905141588</v>
+        <v>1.311085156926009</v>
       </c>
       <c r="G14" t="n">
-        <v>1.229304479945856</v>
+        <v>1.337182717896205</v>
       </c>
       <c r="H14" t="n">
-        <v>1.229304479945855</v>
+        <v>1.337182717896206</v>
       </c>
       <c r="I14" t="n">
         <v>896.6548282456465</v>
@@ -2569,16 +2569,16 @@
         <v>896.6548282456466</v>
       </c>
       <c r="K14" t="n">
-        <v>581.1751781226151</v>
+        <v>598.0143519592931</v>
       </c>
       <c r="L14" t="n">
-        <v>581.1735120220202</v>
+        <v>598.0143519592929</v>
       </c>
       <c r="M14" t="n">
-        <v>881.5683619073927</v>
+        <v>898.4092018446654</v>
       </c>
       <c r="N14" t="n">
-        <v>881.5683619073926</v>
+        <v>898.4092018446653</v>
       </c>
       <c r="O14" t="n">
         <v>0.02041703055851675</v>
@@ -2587,16 +2587,16 @@
         <v>0.02041703055851676</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01855436247795308</v>
+        <v>0.02003197000184767</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01855435105705928</v>
+        <v>0.02003197000184768</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02061351704140056</v>
+        <v>0.02211977487946354</v>
       </c>
       <c r="T14" t="n">
-        <v>0.02061351704140054</v>
+        <v>0.02211977487946356</v>
       </c>
       <c r="U14" t="n">
         <v>3.836516818567063</v>
@@ -2605,16 +2605,16 @@
         <v>3.836516818567063</v>
       </c>
       <c r="W14" t="n">
-        <v>1.50438253330024</v>
+        <v>1.52276405964309</v>
       </c>
       <c r="X14" t="n">
-        <v>1.504376405663195</v>
+        <v>1.52276405964309</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.109231807499004</v>
+        <v>4.240745472963182</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.109231807499004</v>
+        <v>4.240745472963182</v>
       </c>
       <c r="AA14" t="n">
         <v>0.2151801336872796</v>
@@ -2623,16 +2623,16 @@
         <v>0.2151801336872796</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.1394710077776911</v>
+        <v>0.143512089767345</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.1394706079451831</v>
+        <v>0.1435120897673449</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.2115596682179912</v>
+        <v>0.215601150040153</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.2115596682179911</v>
+        <v>0.2156011500401529</v>
       </c>
       <c r="AG14" t="n">
         <v>0.01469376702111024</v>
@@ -2641,16 +2641,16 @@
         <v>0.01469376702111024</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.009523646290038726</v>
+        <v>0.009797726006443941</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.009523619023347505</v>
+        <v>0.009797726006443937</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.01444821479277915</v>
+        <v>0.01472232177587558</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01444821479277915</v>
+        <v>0.01472232177587558</v>
       </c>
     </row>
     <row r="15">
@@ -2669,16 +2669,16 @@
         <v>2.410241413919331</v>
       </c>
       <c r="E15" t="n">
-        <v>2.439651908550792</v>
+        <v>2.589407091208072</v>
       </c>
       <c r="F15" t="n">
-        <v>2.439651908550791</v>
+        <v>2.589407091208066</v>
       </c>
       <c r="G15" t="n">
-        <v>2.122365661439178</v>
+        <v>2.308659720491474</v>
       </c>
       <c r="H15" t="n">
-        <v>2.122365661439166</v>
+        <v>2.308659720491463</v>
       </c>
       <c r="I15" t="n">
         <v>423.8653379596064</v>
@@ -2687,16 +2687,16 @@
         <v>423.8653379595651</v>
       </c>
       <c r="K15" t="n">
-        <v>366.6409866467207</v>
+        <v>396.9687143134287</v>
       </c>
       <c r="L15" t="n">
-        <v>366.6409866466675</v>
+        <v>396.9687143133694</v>
       </c>
       <c r="M15" t="n">
-        <v>410.1559881853913</v>
+        <v>425.4595695552857</v>
       </c>
       <c r="N15" t="n">
-        <v>410.1559881853499</v>
+        <v>425.4595695552444</v>
       </c>
       <c r="O15" t="n">
         <v>0.2079082797955517</v>
@@ -2705,16 +2705,16 @@
         <v>0.2079082797955503</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.209851916968827</v>
+        <v>0.2238497146534855</v>
       </c>
       <c r="R15" t="n">
-        <v>0.209851916968826</v>
+        <v>0.2238497146534841</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2035436216765865</v>
+        <v>0.2196809200500456</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2035436216765855</v>
+        <v>0.2196809200500446</v>
       </c>
       <c r="U15" t="n">
         <v>0.8541606207943468</v>
@@ -2723,16 +2723,16 @@
         <v>0.854160620794243</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5639980441006247</v>
+        <v>0.6350142876169854</v>
       </c>
       <c r="X15" t="n">
-        <v>0.5639980441004906</v>
+        <v>0.6350142876168259</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.7150743687008665</v>
+        <v>0.7301711808324448</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.7150743687007772</v>
+        <v>0.7301711808323554</v>
       </c>
       <c r="AA15" t="n">
         <v>0.1017196330342683</v>
@@ -2741,16 +2741,16 @@
         <v>0.1017196330342584</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.08798687525749183</v>
+        <v>0.09526495405457135</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.08798687525747903</v>
+        <v>0.09526495405455711</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.09842964939256633</v>
+        <v>0.1021022183470112</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.09842964939255643</v>
+        <v>0.1021022183470013</v>
       </c>
       <c r="AG15" t="n">
         <v>0.02283467586414214</v>
@@ -2759,16 +2759,16 @@
         <v>0.02283467586414139</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.02170134256548653</v>
+        <v>0.02235721854914812</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.02170134256548556</v>
+        <v>0.02235721854914705</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.02249152553461129</v>
+        <v>0.02287458009785238</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.02249152553461055</v>
+        <v>0.02287458009785163</v>
       </c>
     </row>
     <row r="16">
@@ -2787,16 +2787,16 @@
         <v>1.341212437336329</v>
       </c>
       <c r="E16" t="n">
-        <v>1.479705081167416</v>
+        <v>1.560201972163842</v>
       </c>
       <c r="F16" t="n">
-        <v>1.479705081167424</v>
+        <v>1.560201972163854</v>
       </c>
       <c r="G16" t="n">
-        <v>1.114410334624249</v>
+        <v>1.215024030649369</v>
       </c>
       <c r="H16" t="n">
-        <v>1.114410334624251</v>
+        <v>1.215024030649374</v>
       </c>
       <c r="I16" t="n">
         <v>445.312118147967</v>
@@ -2805,16 +2805,16 @@
         <v>445.3121181480039</v>
       </c>
       <c r="K16" t="n">
-        <v>331.9456072546465</v>
+        <v>357.9438010729212</v>
       </c>
       <c r="L16" t="n">
-        <v>331.945607254687</v>
+        <v>357.9438010729665</v>
       </c>
       <c r="M16" t="n">
-        <v>431.2234164788381</v>
+        <v>446.950463781636</v>
       </c>
       <c r="N16" t="n">
-        <v>431.2234164788749</v>
+        <v>446.9504637816727</v>
       </c>
       <c r="O16" t="n">
         <v>0.01838410030746193</v>
@@ -2823,16 +2823,16 @@
         <v>0.0183841003074624</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.02033669968530184</v>
+        <v>0.02146407131419055</v>
       </c>
       <c r="R16" t="n">
-        <v>0.02033669968530218</v>
+        <v>0.02146407131419094</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0165628239305196</v>
+        <v>0.01795907425309948</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01656282393051984</v>
+        <v>0.01795907425309975</v>
       </c>
       <c r="U16" t="n">
         <v>1.021969356141318</v>
@@ -2841,16 +2841,16 @@
         <v>1.02196935614142</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5124812175232898</v>
+        <v>0.5642555562732015</v>
       </c>
       <c r="X16" t="n">
-        <v>0.512481217523389</v>
+        <v>0.5642555562733171</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.8395391510193317</v>
+        <v>0.8561571254415866</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.8395391510194179</v>
+        <v>0.8561571254416726</v>
       </c>
       <c r="AA16" t="n">
         <v>0.1068664530621295</v>
@@ -2859,16 +2859,16 @@
         <v>0.1068664530621384</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.07966064297642045</v>
+        <v>0.08589971585621492</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.07966064297643019</v>
+        <v>0.08589971585622577</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.1034854321685323</v>
+        <v>0.1072596249063816</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1034854321685411</v>
+        <v>0.1072596249063904</v>
       </c>
       <c r="AG16" t="n">
         <v>0.03636072401972167</v>
@@ -2877,16 +2877,16 @@
         <v>0.0363607240197223</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.03442866030632046</v>
+        <v>0.03486080317503514</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.03442866030632116</v>
+        <v>0.03486080317503592</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.03613141173335978</v>
+        <v>0.03638739026562075</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.03613141173336042</v>
+        <v>0.03638739026562137</v>
       </c>
     </row>
     <row r="17">
@@ -2903,16 +2903,16 @@
         <v>22.41416778264804</v>
       </c>
       <c r="E17" t="n">
-        <v>23.33770314995289</v>
+        <v>22.94327126929209</v>
       </c>
       <c r="F17" t="n">
-        <v>23.33770300719163</v>
+        <v>22.94327126929201</v>
       </c>
       <c r="G17" t="n">
-        <v>21.94877074704628</v>
+        <v>21.31312804967991</v>
       </c>
       <c r="H17" t="n">
-        <v>21.94877074704612</v>
+        <v>21.31312804967976</v>
       </c>
       <c r="I17" t="n">
         <v>7702.951816940053</v>
@@ -2921,16 +2921,16 @@
         <v>7702.95181693998</v>
       </c>
       <c r="K17" t="n">
-        <v>6385.836677226731</v>
+        <v>6047.161220537516</v>
       </c>
       <c r="L17" t="n">
-        <v>6385.835011126059</v>
+        <v>6047.161220537442</v>
       </c>
       <c r="M17" t="n">
-        <v>7708.835474860139</v>
+        <v>7661.823341622828</v>
       </c>
       <c r="N17" t="n">
-        <v>7708.835474860065</v>
+        <v>7661.823341622754</v>
       </c>
       <c r="O17" t="n">
         <v>1.227822241879152</v>
@@ -2939,16 +2939,16 @@
         <v>1.227822241879149</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.252468181913424</v>
+        <v>1.203898409654131</v>
       </c>
       <c r="R17" t="n">
-        <v>1.252468170492528</v>
+        <v>1.203898409654129</v>
       </c>
       <c r="S17" t="n">
-        <v>1.237476793718553</v>
+        <v>1.176527737589143</v>
       </c>
       <c r="T17" t="n">
-        <v>1.23747679371855</v>
+        <v>1.17652773758914</v>
       </c>
       <c r="U17" t="n">
         <v>31.84088970009331</v>
@@ -2957,16 +2957,16 @@
         <v>31.84088970009263</v>
       </c>
       <c r="W17" t="n">
-        <v>18.72134446485447</v>
+        <v>16.61457596321196</v>
       </c>
       <c r="X17" t="n">
-        <v>18.7213383372177</v>
+        <v>16.614575963212</v>
       </c>
       <c r="Y17" t="n">
-        <v>30.05600124882837</v>
+        <v>30.14120745540007</v>
       </c>
       <c r="Z17" t="n">
-        <v>30.05600124882807</v>
+        <v>30.14120745539971</v>
       </c>
       <c r="AA17" t="n">
         <v>1.84856217748681</v>
@@ -2975,34 +2975,34 @@
         <v>1.848562177486793</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.532479552470924</v>
+        <v>1.451203873412158</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.532479152638397</v>
+        <v>1.45120387341214</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.849974143672607</v>
+        <v>1.838692124331093</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.849974143672589</v>
+        <v>1.838692124331076</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.32198058248425</v>
+        <v>0.3219438746866928</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.3219805824842527</v>
+        <v>0.3219438746866953</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.2916112707090255</v>
+        <v>0.2832440172940929</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.291611243442336</v>
+        <v>0.2832440172940944</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.3222922906539849</v>
+        <v>0.3210750171147053</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.3222922906539875</v>
+        <v>0.3210750171147078</v>
       </c>
     </row>
   </sheetData>
@@ -3594,55 +3594,55 @@
         <v>5.054028754711718</v>
       </c>
       <c r="C4" t="n">
-        <v>5.437107406865588</v>
+        <v>5.140567162988297</v>
       </c>
       <c r="D4" t="n">
-        <v>5.208401435619599</v>
+        <v>4.713981947795547</v>
       </c>
       <c r="E4" t="n">
         <v>1572.242933770302</v>
       </c>
       <c r="F4" t="n">
-        <v>1464.487332618419</v>
+        <v>1277.681153071919</v>
       </c>
       <c r="G4" t="n">
-        <v>1605.072407822223</v>
+        <v>1548.175819217922</v>
       </c>
       <c r="H4" t="n">
         <v>0.2467542011906818</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2588073092156627</v>
+        <v>0.2428953050261933</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2530883265058974</v>
+        <v>0.2270873687757124</v>
       </c>
       <c r="K4" t="n">
         <v>6.279609463525389</v>
       </c>
       <c r="L4" t="n">
-        <v>4.425848836510652</v>
+        <v>3.253704451062037</v>
       </c>
       <c r="M4" t="n">
-        <v>5.640548994126923</v>
+        <v>5.586936673264733</v>
       </c>
       <c r="N4" t="n">
         <v>0.3773084513909402</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3514491531069152</v>
+        <v>0.3066192169685313</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3851869018189573</v>
+        <v>0.3715328008688984</v>
       </c>
       <c r="Q4" t="n">
         <v>0.07092826674974148</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06914800496101803</v>
+        <v>0.06581544824206162</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07155448335404842</v>
+        <v>0.07046919065468674</v>
       </c>
     </row>
     <row r="5">
@@ -3655,55 +3655,55 @@
         <v>2.345789062664478</v>
       </c>
       <c r="C5" t="n">
-        <v>2.326634843410293</v>
+        <v>2.071947412424934</v>
       </c>
       <c r="D5" t="n">
-        <v>2.364219089796864</v>
+        <v>2.12107909846831</v>
       </c>
       <c r="E5" t="n">
         <v>684.9000076076563</v>
       </c>
       <c r="F5" t="n">
-        <v>545.5513858679956</v>
+        <v>481.8056777341648</v>
       </c>
       <c r="G5" t="n">
-        <v>696.0684395495034</v>
+        <v>676.7124889623747</v>
       </c>
       <c r="H5" t="n">
         <v>0.2216070221405289</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2230321082553342</v>
+        <v>0.19862292903492</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2262018639746835</v>
+        <v>0.2027665652072529</v>
       </c>
       <c r="K5" t="n">
         <v>3.321360497066342</v>
       </c>
       <c r="L5" t="n">
-        <v>1.933417175668677</v>
+        <v>1.584143183482866</v>
       </c>
       <c r="M5" t="n">
-        <v>3.338619877407057</v>
+        <v>3.316159485664065</v>
       </c>
       <c r="N5" t="n">
         <v>0.1643629973953133</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1309219740377012</v>
+        <v>0.1156242144471287</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1670432090025223</v>
+        <v>0.1623981483796605</v>
       </c>
       <c r="Q5" t="n">
         <v>0.02467646364099519</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0190097502344173</v>
+        <v>0.01678344606828333</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02495601381400163</v>
+        <v>0.02447152688123343</v>
       </c>
     </row>
     <row r="6">
@@ -3716,55 +3716,55 @@
         <v>2.610400110726969</v>
       </c>
       <c r="C6" t="n">
-        <v>2.860953057140761</v>
+        <v>2.728343525100137</v>
       </c>
       <c r="D6" t="n">
-        <v>2.658939057826277</v>
+        <v>2.483309487491448</v>
       </c>
       <c r="E6" t="n">
         <v>1305.977125956735</v>
       </c>
       <c r="F6" t="n">
-        <v>1158.013731975373</v>
+        <v>1039.736618539127</v>
       </c>
       <c r="G6" t="n">
-        <v>1323.208748205005</v>
+        <v>1297.218776547726</v>
       </c>
       <c r="H6" t="n">
         <v>0.03885712549890564</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04178257969667305</v>
+        <v>0.03967874973662251</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03938003825985255</v>
+        <v>0.03709484844694846</v>
       </c>
       <c r="K6" t="n">
         <v>6.159818949229413</v>
       </c>
       <c r="L6" t="n">
-        <v>4.185162418966212</v>
+        <v>3.300612824113464</v>
       </c>
       <c r="M6" t="n">
-        <v>5.767737518547957</v>
+        <v>5.758530764633043</v>
       </c>
       <c r="N6" t="n">
         <v>0.3134097131955792</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2779013080715838</v>
+        <v>0.2495170466148613</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3175449753524632</v>
+        <v>0.3113078756351907</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05061001706686115</v>
+        <v>0.05060932157513034</v>
       </c>
       <c r="R6" t="n">
-        <v>0.04809645088995405</v>
+        <v>0.04612976944696906</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05089048454983253</v>
+        <v>0.05046676783420354</v>
       </c>
     </row>
     <row r="7">
@@ -3777,55 +3777,55 @@
         <v>4.861441902291737</v>
       </c>
       <c r="C7" t="n">
-        <v>4.9172719597686</v>
+        <v>4.678515474041527</v>
       </c>
       <c r="D7" t="n">
-        <v>4.936968917740872</v>
+        <v>4.611806907491417</v>
       </c>
       <c r="E7" t="n">
         <v>1376.932636236661</v>
       </c>
       <c r="F7" t="n">
-        <v>1146.946138883296</v>
+        <v>1030.597108225773</v>
       </c>
       <c r="G7" t="n">
-        <v>1393.646451703689</v>
+        <v>1368.437473465052</v>
       </c>
       <c r="H7" t="n">
         <v>0.4372762605957713</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4420487266599126</v>
+        <v>0.4165064063911494</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4432745049190295</v>
+        <v>0.4121501455760118</v>
       </c>
       <c r="K7" t="n">
         <v>5.449922017049271</v>
       </c>
       <c r="L7" t="n">
-        <v>3.480744964644968</v>
+        <v>2.907871327941082</v>
       </c>
       <c r="M7" t="n">
-        <v>5.621930608229398</v>
+        <v>5.593118589174506</v>
       </c>
       <c r="N7" t="n">
         <v>0.3304376884062373</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2752452958736577</v>
+        <v>0.2473237376746623</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3344486867673974</v>
+        <v>0.3283990106416101</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0563644592620564</v>
+        <v>0.05632844695622995</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04766603121742205</v>
+        <v>0.04424568857244508</v>
       </c>
       <c r="S7" t="n">
-        <v>0.05678281253042331</v>
+        <v>0.0561158097449467</v>
       </c>
     </row>
     <row r="8">
@@ -3838,55 +3838,55 @@
         <v>2.551072298886052</v>
       </c>
       <c r="C8" t="n">
-        <v>2.672813845146683</v>
+        <v>2.863203474439272</v>
       </c>
       <c r="D8" t="n">
-        <v>2.314161770053389</v>
+        <v>2.52208413939614</v>
       </c>
       <c r="E8" t="n">
         <v>997.0668290154779</v>
       </c>
       <c r="F8" t="n">
-        <v>791.0763158576647</v>
+        <v>864.413795620889</v>
       </c>
       <c r="G8" t="n">
-        <v>967.8916610080951</v>
+        <v>1000.459548248166</v>
       </c>
       <c r="H8" t="n">
         <v>0.03661822179173395</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03805447895375963</v>
+        <v>0.04084926349572157</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0348120974105829</v>
+        <v>0.03766904040060824</v>
       </c>
       <c r="K8" t="n">
         <v>4.917531977720173</v>
       </c>
       <c r="L8" t="n">
-        <v>2.115309274139806</v>
+        <v>2.846210273079234</v>
       </c>
       <c r="M8" t="n">
-        <v>4.023318923297837</v>
+        <v>4.059388163426512</v>
       </c>
       <c r="N8" t="n">
         <v>0.2392771073150625</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1898432953694624</v>
+        <v>0.2074428980288434</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2322756209521769</v>
+        <v>0.240091295512188</v>
       </c>
       <c r="Q8" t="n">
         <v>0.04551220885962178</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04203738424436843</v>
+        <v>0.04325391723370661</v>
       </c>
       <c r="S8" t="n">
-        <v>0.04503734434492879</v>
+        <v>0.04556742986028619</v>
       </c>
     </row>
     <row r="9">
@@ -3899,55 +3899,55 @@
         <v>3.650223216030941</v>
       </c>
       <c r="C9" t="n">
-        <v>3.643216956453553</v>
+        <v>3.900492248134079</v>
       </c>
       <c r="D9" t="n">
-        <v>3.351670141385034</v>
+        <v>3.645842438387679</v>
       </c>
       <c r="E9" t="n">
         <v>1320.520166205253</v>
       </c>
       <c r="F9" t="n">
-        <v>947.8161647693357</v>
+        <v>994.9830662727218</v>
       </c>
       <c r="G9" t="n">
-        <v>1291.724350092784</v>
+        <v>1323.868771399951</v>
       </c>
       <c r="H9" t="n">
         <v>0.2283253103540685</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2284062794467801</v>
+        <v>0.2438816846553332</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2241571387179871</v>
+        <v>0.2418006949295092</v>
       </c>
       <c r="K9" t="n">
         <v>4.69067743936141</v>
       </c>
       <c r="L9" t="n">
-        <v>2.068380577400865</v>
+        <v>2.157778347260076</v>
       </c>
       <c r="M9" t="n">
-        <v>4.824306176199871</v>
+        <v>4.970916653795626</v>
       </c>
       <c r="N9" t="n">
         <v>0.316899766721548</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2274578830351829</v>
+        <v>0.2387770438219163</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3099893176105575</v>
+        <v>0.3177033683871642</v>
       </c>
       <c r="Q9" t="n">
         <v>0.03752844288525238</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03122498885552526</v>
+        <v>0.03215494455559206</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03693974032739044</v>
+        <v>0.03759690187372796</v>
       </c>
     </row>
     <row r="10">
@@ -3960,55 +3960,55 @@
         <v>1.341212437336297</v>
       </c>
       <c r="C10" t="n">
-        <v>1.479705081167416</v>
+        <v>1.560201972163842</v>
       </c>
       <c r="D10" t="n">
-        <v>1.114410334624249</v>
+        <v>1.215024030649369</v>
       </c>
       <c r="E10" t="n">
         <v>445.312118147967</v>
       </c>
       <c r="F10" t="n">
-        <v>331.9456072546465</v>
+        <v>357.9438010729212</v>
       </c>
       <c r="G10" t="n">
-        <v>431.2234164788381</v>
+        <v>446.950463781636</v>
       </c>
       <c r="H10" t="n">
         <v>0.01838410030746193</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02033669968530184</v>
+        <v>0.02146407131419055</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0165628239305196</v>
+        <v>0.01795907425309948</v>
       </c>
       <c r="K10" t="n">
         <v>1.021969356141318</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5124812175232898</v>
+        <v>0.5642555562732015</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8395391510193317</v>
+        <v>0.8561571254415866</v>
       </c>
       <c r="N10" t="n">
         <v>0.1068664530621295</v>
       </c>
       <c r="O10" t="n">
-        <v>0.07966064297642045</v>
+        <v>0.08589971585621492</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1034854321685323</v>
+        <v>0.1072596249063816</v>
       </c>
       <c r="Q10" t="n">
         <v>0.03636072401972167</v>
       </c>
       <c r="R10" t="n">
-        <v>0.03442866030632046</v>
+        <v>0.03486080317503514</v>
       </c>
       <c r="S10" t="n">
-        <v>0.03613141173335978</v>
+        <v>0.03638739026562075</v>
       </c>
     </row>
   </sheetData>
